--- a/logs/feature_importance_analysis/yaw_angle/yaw_angle_feature_importance_analysis.xlsx
+++ b/logs/feature_importance_analysis/yaw_angle/yaw_angle_feature_importance_analysis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/feature_importance_analysis/yaw_rate/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/feature_importance_analysis/yaw_angle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_61CD53A5D350D66747182211595ED87656CFA2FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3237872-8400-4BEA-9D12-2CE00C96AEFE}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_61CD53A5D350D66747182211595ED87656CFA2FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EFEDD9E-BA02-49C8-81DE-C8038586506E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,13 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="20" r:id="rId3"/>
+    <pivotCache cacheId="8" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="262">
   <si>
     <t>date</t>
   </si>
@@ -615,6 +615,201 @@
   </si>
   <si>
     <t>Promedio de global closed R2</t>
+  </si>
+  <si>
+    <t>15/04/2026 23:18:16</t>
+  </si>
+  <si>
+    <t>04-15_23-18-16_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>['ya', 'yr', 'wv']</t>
+  </si>
+  <si>
+    <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+  </si>
+  <si>
+    <t>[0, 1, 2]</t>
+  </si>
+  <si>
+    <t>15/04/2026 23:39:40</t>
+  </si>
+  <si>
+    <t>04-15_23-39-40_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 23:40:19</t>
+  </si>
+  <si>
+    <t>04-15_23-40-19_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 23:59:38</t>
+  </si>
+  <si>
+    <t>04-15_23-59-38_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 00:20:53</t>
+  </si>
+  <si>
+    <t>04-16_00-20-53_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 00:21:27</t>
+  </si>
+  <si>
+    <t>04-16_00-21-27_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 00:23:04</t>
+  </si>
+  <si>
+    <t>04-16_00-23-04_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 00:23:22</t>
+  </si>
+  <si>
+    <t>04-16_00-23-22_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 00:41:05</t>
+  </si>
+  <si>
+    <t>04-16_00-41-05_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 01:02:07</t>
+  </si>
+  <si>
+    <t>04-16_01-02-07_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 01:02:59</t>
+  </si>
+  <si>
+    <t>04-16_01-02-59_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+  </si>
+  <si>
+    <t>16/04/2026 01:07:41</t>
+  </si>
+  <si>
+    <t>04-16_01-07-41_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 01:07:50</t>
+  </si>
+  <si>
+    <t>04-16_01-07-50_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 01:22:18</t>
+  </si>
+  <si>
+    <t>04-16_01-22-18_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 01:43:21</t>
+  </si>
+  <si>
+    <t>04-16_01-43-21_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 02:04:53</t>
+  </si>
+  <si>
+    <t>04-16_02-04-53_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 02:13:51</t>
+  </si>
+  <si>
+    <t>04-16_02-13-51_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 02:14:15</t>
+  </si>
+  <si>
+    <t>04-16_02-14-15_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 02:24:01</t>
+  </si>
+  <si>
+    <t>04-16_02-24-01_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 02:44:46</t>
+  </si>
+  <si>
+    <t>04-16_02-44-46_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 03:06:18</t>
+  </si>
+  <si>
+    <t>04-16_03-06-18_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+  </si>
+  <si>
+    <t>16/04/2026 03:20:20</t>
+  </si>
+  <si>
+    <t>04-16_03-20-20_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 03:20:42</t>
+  </si>
+  <si>
+    <t>04-16_03-20-42_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 03:25:49</t>
+  </si>
+  <si>
+    <t>04-16_03-25-49_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 03:45:58</t>
+  </si>
+  <si>
+    <t>04-16_03-45-58_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 04:28:13</t>
+  </si>
+  <si>
+    <t>04-16_04-28-13_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 04:46:45</t>
+  </si>
+  <si>
+    <t>04-16_04-46-45_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 04:48:01</t>
+  </si>
+  <si>
+    <t>04-16_04-48-01_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 04:48:32</t>
+  </si>
+  <si>
+    <t>04-16_04-48-32_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>16/04/2026 05:04:22</t>
+  </si>
+  <si>
+    <t>04-16_05-04-22_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
   </si>
 </sst>
 </file>
@@ -685,6 +880,20 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -713,20 +922,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -741,7 +936,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46126.416322453704" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="50" xr:uid="{FB6810C7-6835-46AB-80A6-4693E5374205}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46128.432197337963" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="80" xr:uid="{FB6810C7-6835-46AB-80A6-4693E5374205}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
@@ -779,12 +974,13 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="4.5" maxValue="4.5"/>
     </cacheField>
     <cacheField name="features" numFmtId="0">
-      <sharedItems count="5">
+      <sharedItems count="6">
         <s v="['ya']"/>
         <s v="['ya', 'rarad']"/>
         <s v="['ya', 'sv']"/>
         <s v="['ya', 'wv']"/>
         <s v="['ya', 'yr']"/>
+        <s v="['ya', 'yr', 'wv']"/>
       </sharedItems>
     </cacheField>
     <cacheField name="targets" numFmtId="0">
@@ -827,10 +1023,18 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="reps" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5" count="3">
+        <n v="1"/>
+        <n v="3"/>
+        <n v="5"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="map" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="3">
+        <s v="[0, -1, -1]"/>
+        <s v="[0, 1, -1]"/>
+        <s v="[0, 1, 2]"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="reorder" numFmtId="0">
       <sharedItems/>
@@ -860,16 +1064,16 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="total params" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="40" maxValue="40"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="40" maxValue="80"/>
     </cacheField>
     <cacheField name="q params" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10" maxValue="10"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10" maxValue="50"/>
     </cacheField>
     <cacheField name="c params" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="30" maxValue="30"/>
     </cacheField>
     <cacheField name="final val loss" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.2652376921493302E-2" maxValue="0.1516467495252215"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.2361351023914103E-2" maxValue="0.1516467495252215"/>
     </cacheField>
     <cacheField name="Val Global Open MSE" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="4.8477262874784968" maxValue="142.59517720900129"/>
@@ -1001,7 +1205,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="50">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="80">
   <r>
     <s v="13/04/2026 17:04:48"/>
     <s v="04-13_17-04-48_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
@@ -1024,8 +1228,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1102,8 +1306,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1180,8 +1384,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1258,8 +1462,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1336,8 +1540,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1414,8 +1618,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1492,8 +1696,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1570,8 +1774,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1648,8 +1852,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1726,8 +1930,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1804,8 +2008,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1882,8 +2086,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1960,8 +2164,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2038,8 +2242,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2116,8 +2320,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2194,8 +2398,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2272,8 +2476,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2350,8 +2554,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2428,8 +2632,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2506,8 +2710,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2584,8 +2788,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2662,8 +2866,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2740,8 +2944,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2818,8 +3022,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2896,8 +3100,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2974,8 +3178,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3052,8 +3256,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3130,8 +3334,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3208,8 +3412,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3286,8 +3490,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3364,8 +3568,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3442,8 +3646,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3520,8 +3724,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3598,8 +3802,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3676,8 +3880,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3754,8 +3958,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3832,8 +4036,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3910,8 +4114,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3988,8 +4192,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4066,8 +4270,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4144,8 +4348,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4222,8 +4426,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4300,8 +4504,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4378,8 +4582,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4456,8 +4660,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4534,8 +4738,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4612,8 +4816,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4690,8 +4894,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4768,8 +4972,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4846,8 +5050,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4902,15 +5106,2355 @@
     <n v="1590.422072265764"/>
     <n v="-3.5266215766945019"/>
   </r>
+  <r>
+    <s v="15/04/2026 23:18:16"/>
+    <s v="04-15_23-18-16_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="0"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="5.7150730328352703E-2"/>
+    <n v="5.2629089424840103"/>
+    <n v="0.98422075820972799"/>
+    <n v="-3.6370012570852581"/>
+    <n v="8.1888289403937069"/>
+    <n v="0.97669314931184359"/>
+    <n v="8.1888289403937069"/>
+    <n v="8.1888289403937069"/>
+    <n v="0.97669314931184359"/>
+    <n v="1570.8733875388079"/>
+    <n v="-3.4709825739265319"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="8.1888289403937069"/>
+    <n v="0.97669314931184359"/>
+    <n v="8.1888289403937069"/>
+    <n v="8.1888289403937069"/>
+    <n v="0.97669314931184359"/>
+    <n v="1570.8733875388079"/>
+    <n v="-3.4709825739265319"/>
+  </r>
+  <r>
+    <s v="15/04/2026 23:39:40"/>
+    <s v="04-15_23-39-40_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="1"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="7.4276302489280605E-2"/>
+    <n v="5.32380974050532"/>
+    <n v="0.9840381655736592"/>
+    <n v="-3.8512886290860249"/>
+    <n v="8.0535178159390473"/>
+    <n v="0.97707826862463742"/>
+    <n v="8.0535178159390473"/>
+    <n v="8.0535178159390473"/>
+    <n v="0.97707826862463742"/>
+    <n v="1637.0723537957961"/>
+    <n v="-3.6593965014236862"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="8.0535178159390473"/>
+    <n v="0.97707826862463742"/>
+    <n v="8.0535178159390473"/>
+    <n v="8.0535178159390473"/>
+    <n v="0.97707826862463742"/>
+    <n v="1637.0723537957961"/>
+    <n v="-3.6593965014236862"/>
+  </r>
+  <r>
+    <s v="15/04/2026 23:40:19"/>
+    <s v="04-15_23-40-19_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="2"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="5.1604037359194797E-2"/>
+    <n v="4.9834633784533731"/>
+    <n v="0.98505859127320061"/>
+    <n v="-3.7548451378461132"/>
+    <n v="7.716047078567998"/>
+    <n v="0.97803876983241478"/>
+    <n v="7.716047078567998"/>
+    <n v="7.716047078567998"/>
+    <n v="0.97803876983241478"/>
+    <n v="1609.0161075963031"/>
+    <n v="-3.5795434789950238"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="7.716047078567998"/>
+    <n v="0.97803876983241478"/>
+    <n v="7.716047078567998"/>
+    <n v="7.716047078567998"/>
+    <n v="0.97803876983241478"/>
+    <n v="1609.0161075963031"/>
+    <n v="-3.5795434789950238"/>
+  </r>
+  <r>
+    <s v="15/04/2026 23:59:38"/>
+    <s v="04-15_23-59-38_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="3"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="5.1529209445481998E-2"/>
+    <n v="5.6807518930531371"/>
+    <n v="0.98296798241226602"/>
+    <n v="-3.6395890215677742"/>
+    <n v="8.3530439583657721"/>
+    <n v="0.97622576442293119"/>
+    <n v="8.3530439583657721"/>
+    <n v="8.3530439583657721"/>
+    <n v="0.97622576442293119"/>
+    <n v="1571.459982038853"/>
+    <n v="-3.4726521252783278"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="8.3530439583657721"/>
+    <n v="0.97622576442293119"/>
+    <n v="8.3530439583657721"/>
+    <n v="8.3530439583657721"/>
+    <n v="0.97622576442293119"/>
+    <n v="1571.459982038853"/>
+    <n v="-3.4726521252783278"/>
+  </r>
+  <r>
+    <s v="16/04/2026 00:20:53"/>
+    <s v="04-16_00-20-53_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="4"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="3.2361351023914103E-2"/>
+    <n v="6.1346238380219011"/>
+    <n v="0.98160718456458318"/>
+    <n v="-3.804297484629116"/>
+    <n v="9.2016147239691684"/>
+    <n v="0.97381058243827723"/>
+    <n v="9.2016147239691684"/>
+    <n v="9.2016147239691684"/>
+    <n v="0.97381058243827723"/>
+    <n v="1624.5102171318081"/>
+    <n v="-3.623642446029081"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="9.2016147239691684"/>
+    <n v="0.97381058243827723"/>
+    <n v="9.2016147239691684"/>
+    <n v="9.2016147239691684"/>
+    <n v="0.97381058243827723"/>
+    <n v="1624.5102171318081"/>
+    <n v="-3.623642446029081"/>
+  </r>
+  <r>
+    <s v="16/04/2026 00:21:27"/>
+    <s v="04-16_00-21-27_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="5"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="7.2798951399546494E-2"/>
+    <n v="5.33760499111815"/>
+    <n v="0.98399680468420503"/>
+    <n v="-3.667662959479729"/>
+    <n v="8.2460592780144673"/>
+    <n v="0.97653026168243162"/>
+    <n v="8.2460592780144673"/>
+    <n v="8.2460592780144673"/>
+    <n v="0.97653026168243162"/>
+    <n v="1582.088118269746"/>
+    <n v="-3.502901674515448"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="8.2460592780144673"/>
+    <n v="0.97653026168243162"/>
+    <n v="8.2460592780144673"/>
+    <n v="8.2460592780144673"/>
+    <n v="0.97653026168243162"/>
+    <n v="1582.088118269746"/>
+    <n v="-3.502901674515448"/>
+  </r>
+  <r>
+    <s v="16/04/2026 00:23:04"/>
+    <s v="04-16_00-23-04_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="6"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="5.3524819002593302E-2"/>
+    <n v="6.4125991309808636"/>
+    <n v="0.98077375966454095"/>
+    <n v="-3.315272679274432"/>
+    <n v="10.240591082057311"/>
+    <n v="0.97085347257278265"/>
+    <n v="10.240591082057311"/>
+    <n v="10.240591082057311"/>
+    <n v="0.97085347257278265"/>
+    <n v="1471.6420377514889"/>
+    <n v="-3.188552659965469"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="10.240591082057311"/>
+    <n v="0.97085347257278265"/>
+    <n v="10.240591082057311"/>
+    <n v="10.240591082057311"/>
+    <n v="0.97085347257278265"/>
+    <n v="1471.6420377514889"/>
+    <n v="-3.188552659965469"/>
+  </r>
+  <r>
+    <s v="16/04/2026 00:23:22"/>
+    <s v="04-16_00-23-22_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="7"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="5.5301536648489497E-2"/>
+    <n v="5.3794103542524301"/>
+    <n v="0.98387146393819658"/>
+    <n v="-3.7503506951755821"/>
+    <n v="8.2290284715517448"/>
+    <n v="0.97657873435980902"/>
+    <n v="8.2290284715517448"/>
+    <n v="8.2290284715517448"/>
+    <n v="0.97657873435980902"/>
+    <n v="1607.6479781961821"/>
+    <n v="-3.5756495415489238"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="8.2290284715517448"/>
+    <n v="0.97657873435980902"/>
+    <n v="8.2290284715517448"/>
+    <n v="8.2290284715517448"/>
+    <n v="0.97657873435980902"/>
+    <n v="1607.6479781961821"/>
+    <n v="-3.5756495415489238"/>
+  </r>
+  <r>
+    <s v="16/04/2026 00:41:05"/>
+    <s v="04-16_00-41-05_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="8"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="5.5489815718812903E-2"/>
+    <n v="5.4546171420801723"/>
+    <n v="0.98364597911556839"/>
+    <n v="-3.6406276373494229"/>
+    <n v="8.2006302906341073"/>
+    <n v="0.97665956058872161"/>
+    <n v="8.2006302906341073"/>
+    <n v="8.2006302906341073"/>
+    <n v="0.97665956058872161"/>
+    <n v="1577.740266855822"/>
+    <n v="-3.490526922953749"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="8.2006302906341073"/>
+    <n v="0.97665956058872161"/>
+    <n v="8.2006302906341073"/>
+    <n v="8.2006302906341073"/>
+    <n v="0.97665956058872161"/>
+    <n v="1577.740266855822"/>
+    <n v="-3.490526922953749"/>
+  </r>
+  <r>
+    <s v="16/04/2026 01:02:07"/>
+    <s v="04-16_01-02-07_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="9"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="4.5530792681009201E-2"/>
+    <n v="5.1988481378496738"/>
+    <n v="0.98441282517053841"/>
+    <n v="-3.705521951131427"/>
+    <n v="7.8935863878005126"/>
+    <n v="0.97753346166177402"/>
+    <n v="7.8935863878005126"/>
+    <n v="7.8935863878005126"/>
+    <n v="0.97753346166177402"/>
+    <n v="1591.074277294965"/>
+    <n v="-3.528477867178077"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="7.8935863878005126"/>
+    <n v="0.97753346166177402"/>
+    <n v="7.8935863878005126"/>
+    <n v="7.8935863878005126"/>
+    <n v="0.97753346166177402"/>
+    <n v="1591.074277294965"/>
+    <n v="-3.528477867178077"/>
+  </r>
+  <r>
+    <s v="16/04/2026 01:02:59"/>
+    <s v="04-16_01-02-59_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="0"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="4.3384309475530902E-2"/>
+    <n v="7.2689830642188591"/>
+    <n v="0.97820615127618682"/>
+    <n v="-0.52769369452162795"/>
+    <n v="10.934054881481099"/>
+    <n v="0.9688797523560756"/>
+    <n v="10.934054881481099"/>
+    <n v="10.934054881481099"/>
+    <n v="0.9688797523560756"/>
+    <n v="542.37491525372229"/>
+    <n v="-0.54369461846546474"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="10.934054881481099"/>
+    <n v="0.9688797523560756"/>
+    <n v="10.934054881481099"/>
+    <n v="10.934054881481099"/>
+    <n v="0.9688797523560756"/>
+    <n v="542.37491525372229"/>
+    <n v="-0.54369461846546474"/>
+  </r>
+  <r>
+    <s v="16/04/2026 01:07:41"/>
+    <s v="04-16_01-07-41_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="1"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="4.7437990433947502E-2"/>
+    <n v="8.5839315542630299"/>
+    <n v="0.97426367566186101"/>
+    <n v="-0.57480940575505923"/>
+    <n v="15.449850579664741"/>
+    <n v="0.9560270017562168"/>
+    <n v="15.449850579664741"/>
+    <n v="15.449850579664741"/>
+    <n v="0.9560270017562168"/>
+    <n v="547.26825314352357"/>
+    <n v="-0.55762192069566785"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="15.449850579664741"/>
+    <n v="0.9560270017562168"/>
+    <n v="15.449850579664741"/>
+    <n v="15.449850579664741"/>
+    <n v="0.9560270017562168"/>
+    <n v="547.26825314352357"/>
+    <n v="-0.55762192069566785"/>
+  </r>
+  <r>
+    <s v="16/04/2026 01:07:50"/>
+    <s v="04-16_01-07-50_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="2"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="4.4807172623616998E-2"/>
+    <n v="13.49298940399798"/>
+    <n v="0.95954534942442482"/>
+    <n v="-0.38436834586904339"/>
+    <n v="17.850014098120869"/>
+    <n v="0.949195713282736"/>
+    <n v="17.850014098120869"/>
+    <n v="17.850014098120869"/>
+    <n v="0.949195713282736"/>
+    <n v="472.59543286102883"/>
+    <n v="-0.3450899108740082"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="17.850014098120869"/>
+    <n v="0.949195713282736"/>
+    <n v="17.850014098120869"/>
+    <n v="17.850014098120869"/>
+    <n v="0.949195713282736"/>
+    <n v="472.59543286102883"/>
+    <n v="-0.3450899108740082"/>
+  </r>
+  <r>
+    <s v="16/04/2026 01:22:18"/>
+    <s v="04-16_01-22-18_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="3"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="4.19660558575232E-2"/>
+    <n v="7.7440577950578726"/>
+    <n v="0.97678178328345078"/>
+    <n v="-1.0310931277351949"/>
+    <n v="10.43612768758244"/>
+    <n v="0.97029694092433638"/>
+    <n v="10.43612768758244"/>
+    <n v="10.43612768758244"/>
+    <n v="0.97029694092433638"/>
+    <n v="690.87274731105333"/>
+    <n v="-0.96634562564461202"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="10.43612768758244"/>
+    <n v="0.97029694092433638"/>
+    <n v="10.43612768758244"/>
+    <n v="10.43612768758244"/>
+    <n v="0.97029694092433638"/>
+    <n v="690.87274731105333"/>
+    <n v="-0.96634562564461202"/>
+  </r>
+  <r>
+    <s v="16/04/2026 01:43:21"/>
+    <s v="04-16_01-43-21_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="4"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="4.9762633438750203E-2"/>
+    <n v="13.840749641855581"/>
+    <n v="0.95850269545906719"/>
+    <n v="-0.38309558443557701"/>
+    <n v="17.936860222398511"/>
+    <n v="0.9489485339038386"/>
+    <n v="17.936860222398511"/>
+    <n v="17.936860222398511"/>
+    <n v="0.9489485339038386"/>
+    <n v="482.15050878280817"/>
+    <n v="-0.37228534131271052"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="17.936860222398511"/>
+    <n v="0.9489485339038386"/>
+    <n v="17.936860222398511"/>
+    <n v="17.936860222398511"/>
+    <n v="0.9489485339038386"/>
+    <n v="482.15050878280817"/>
+    <n v="-0.37228534131271052"/>
+  </r>
+  <r>
+    <s v="16/04/2026 02:04:53"/>
+    <s v="04-16_02-04-53_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="5"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="5.2988112802633998E-2"/>
+    <n v="12.02885377924304"/>
+    <n v="0.96393511757151618"/>
+    <n v="-0.45034989442469398"/>
+    <n v="15.056692911027881"/>
+    <n v="0.95714599778684839"/>
+    <n v="15.056692911027881"/>
+    <n v="15.056692911027881"/>
+    <n v="0.95714599778684839"/>
+    <n v="505.06795376309748"/>
+    <n v="-0.43751242960550418"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="15.056692911027881"/>
+    <n v="0.95714599778684839"/>
+    <n v="15.056692911027881"/>
+    <n v="15.056692911027881"/>
+    <n v="0.95714599778684839"/>
+    <n v="505.06795376309748"/>
+    <n v="-0.43751242960550418"/>
+  </r>
+  <r>
+    <s v="16/04/2026 02:13:51"/>
+    <s v="04-16_02-13-51_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="6"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="4.3672558209668803E-2"/>
+    <n v="10.307239191809661"/>
+    <n v="0.96909685856716199"/>
+    <n v="-0.73148871718562547"/>
+    <n v="14.144059823761109"/>
+    <n v="0.95974351243183942"/>
+    <n v="14.144059823761109"/>
+    <n v="14.144059823761109"/>
+    <n v="0.95974351243183942"/>
+    <n v="609.18186437815234"/>
+    <n v="-0.73383897237835716"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="14.144059823761109"/>
+    <n v="0.95974351243183942"/>
+    <n v="14.144059823761109"/>
+    <n v="14.144059823761109"/>
+    <n v="0.95974351243183942"/>
+    <n v="609.18186437815234"/>
+    <n v="-0.73383897237835716"/>
+  </r>
+  <r>
+    <s v="16/04/2026 02:14:15"/>
+    <s v="04-16_02-14-15_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="7"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="5.2030213751537401E-2"/>
+    <n v="8.8771562855018082"/>
+    <n v="0.97338452993016222"/>
+    <n v="-0.22933283932982501"/>
+    <n v="12.28857080051313"/>
+    <n v="0.96502456127693537"/>
+    <n v="12.28857080051313"/>
+    <n v="12.28857080051313"/>
+    <n v="0.96502456127693537"/>
+    <n v="445.82502196278142"/>
+    <n v="-0.26889660237927071"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="12.28857080051313"/>
+    <n v="0.96502456127693537"/>
+    <n v="12.28857080051313"/>
+    <n v="12.28857080051313"/>
+    <n v="0.96502456127693537"/>
+    <n v="445.82502196278142"/>
+    <n v="-0.26889660237927071"/>
+  </r>
+  <r>
+    <s v="16/04/2026 02:24:01"/>
+    <s v="04-16_02-24-01_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="8"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="6.3973457900765196E-2"/>
+    <n v="9.8246069341337474"/>
+    <n v="0.97054388551991377"/>
+    <n v="-5.0574616377070801E-2"/>
+    <n v="13.897281032161761"/>
+    <n v="0.96044588837480704"/>
+    <n v="13.897281032161761"/>
+    <n v="13.897281032161761"/>
+    <n v="0.96044588837480704"/>
+    <n v="373.69727105100691"/>
+    <n v="-6.3608308630586696E-2"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="13.897281032161761"/>
+    <n v="0.96044588837480704"/>
+    <n v="13.897281032161761"/>
+    <n v="13.897281032161761"/>
+    <n v="0.96044588837480704"/>
+    <n v="373.69727105100691"/>
+    <n v="-6.3608308630586696E-2"/>
+  </r>
+  <r>
+    <s v="16/04/2026 02:44:46"/>
+    <s v="04-16_02-44-46_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="9"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="5.3287233628539502E-2"/>
+    <n v="11.450744221834279"/>
+    <n v="0.96566840435023715"/>
+    <n v="-1.16763416628604E-2"/>
+    <n v="18.487639071267509"/>
+    <n v="0.94738092020886155"/>
+    <n v="18.487639071267509"/>
+    <n v="18.487639071267509"/>
+    <n v="0.94738092020886155"/>
+    <n v="355.68093468929771"/>
+    <n v="-1.2330639431922001E-2"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="18.487639071267509"/>
+    <n v="0.94738092020886155"/>
+    <n v="18.487639071267509"/>
+    <n v="18.487639071267509"/>
+    <n v="0.94738092020886155"/>
+    <n v="355.68093468929771"/>
+    <n v="-1.2330639431922001E-2"/>
+  </r>
+  <r>
+    <s v="16/04/2026 03:06:18"/>
+    <s v="04-16_03-06-18_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="0"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="4.75144492153525E-2"/>
+    <n v="14.060896425098811"/>
+    <n v="0.95784265186718498"/>
+    <n v="-0.35488162732929068"/>
+    <n v="16.183668659121409"/>
+    <n v="0.95393842614489821"/>
+    <n v="16.183668659121409"/>
+    <n v="16.183668659121409"/>
+    <n v="0.95393842614489821"/>
+    <n v="460.12175391430992"/>
+    <n v="-0.30958762173604493"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="16.183668659121409"/>
+    <n v="0.95393842614489821"/>
+    <n v="16.183668659121409"/>
+    <n v="16.183668659121409"/>
+    <n v="0.95393842614489821"/>
+    <n v="460.12175391430992"/>
+    <n v="-0.30958762173604493"/>
+  </r>
+  <r>
+    <s v="16/04/2026 03:20:20"/>
+    <s v="04-16_03-20-20_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="1"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="4.7524084001423397E-2"/>
+    <n v="15.450875031102809"/>
+    <n v="0.95367522112742942"/>
+    <n v="-7.5528444953792295E-2"/>
+    <n v="16.225166713169219"/>
+    <n v="0.9538203153678162"/>
+    <n v="16.225166713169219"/>
+    <n v="16.225166713169219"/>
+    <n v="0.9538203153678162"/>
+    <n v="374.74153992916081"/>
+    <n v="-6.6580481941151903E-2"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="16.225166713169219"/>
+    <n v="0.9538203153678162"/>
+    <n v="16.225166713169219"/>
+    <n v="16.225166713169219"/>
+    <n v="0.9538203153678162"/>
+    <n v="374.74153992916081"/>
+    <n v="-6.6580481941151903E-2"/>
+  </r>
+  <r>
+    <s v="16/04/2026 03:20:42"/>
+    <s v="04-16_03-20-42_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="2"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="5.6414274049048897E-2"/>
+    <n v="19.529998713858539"/>
+    <n v="0.94144520164845902"/>
+    <n v="-0.78859905629171378"/>
+    <n v="22.398163909587929"/>
+    <n v="0.9362508771731014"/>
+    <n v="22.398163909587929"/>
+    <n v="22.398163909587929"/>
+    <n v="0.9362508771731014"/>
+    <n v="1527.6475458353959"/>
+    <n v="-3.3479542086029221"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="22.398163909587929"/>
+    <n v="0.9362508771731014"/>
+    <n v="22.398163909587929"/>
+    <n v="22.398163909587929"/>
+    <n v="0.9362508771731014"/>
+    <n v="1527.6475458353959"/>
+    <n v="-3.3479542086029221"/>
+  </r>
+  <r>
+    <s v="16/04/2026 03:25:49"/>
+    <s v="04-16_03-25-49_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="3"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="4.3491384508493901E-2"/>
+    <n v="14.48083916563613"/>
+    <n v="0.9565835804841486"/>
+    <n v="-0.9376424149341448"/>
+    <n v="16.775494814616561"/>
+    <n v="0.95225398457945876"/>
+    <n v="16.775494814616561"/>
+    <n v="16.775494814616561"/>
+    <n v="0.95225398457945876"/>
+    <n v="679.61481649941993"/>
+    <n v="-0.93430357001074238"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="16.775494814616561"/>
+    <n v="0.95225398457945876"/>
+    <n v="16.775494814616561"/>
+    <n v="16.775494814616561"/>
+    <n v="0.95225398457945876"/>
+    <n v="679.61481649941993"/>
+    <n v="-0.93430357001074238"/>
+  </r>
+  <r>
+    <s v="16/04/2026 03:45:58"/>
+    <s v="04-16_03-45-58_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="4"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="5.2385016179553302E-2"/>
+    <n v="16.2596596270809"/>
+    <n v="0.95125032496531525"/>
+    <n v="-0.17970506589140359"/>
+    <n v="20.150111876424312"/>
+    <n v="0.94264922954528219"/>
+    <n v="20.150111876424312"/>
+    <n v="20.150111876424312"/>
+    <n v="0.94264922954528219"/>
+    <n v="416.04593872148291"/>
+    <n v="-0.18414008202854079"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="20.150111876424312"/>
+    <n v="0.94264922954528219"/>
+    <n v="20.150111876424312"/>
+    <n v="20.150111876424312"/>
+    <n v="0.94264922954528219"/>
+    <n v="416.04593872148291"/>
+    <n v="-0.18414008202854079"/>
+  </r>
+  <r>
+    <s v="16/04/2026 04:28:13"/>
+    <s v="04-16_04-28-13_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="5"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="4.54845991199503E-2"/>
+    <n v="18.325743024120921"/>
+    <n v="0.9450557983571134"/>
+    <n v="-0.14442421302849001"/>
+    <n v="18.612661914385601"/>
+    <n v="0.94702508315836598"/>
+    <n v="18.612661914385601"/>
+    <n v="18.612661914385601"/>
+    <n v="0.94702508315836598"/>
+    <n v="394.26644516420419"/>
+    <n v="-0.1221518040832998"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="18.612661914385601"/>
+    <n v="0.94702508315836598"/>
+    <n v="18.612661914385601"/>
+    <n v="18.612661914385601"/>
+    <n v="0.94702508315836598"/>
+    <n v="394.26644516420419"/>
+    <n v="-0.1221518040832998"/>
+  </r>
+  <r>
+    <s v="16/04/2026 04:46:45"/>
+    <s v="04-16_04-46-45_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="6"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="4.7547869048884202E-2"/>
+    <n v="18.49291590390904"/>
+    <n v="0.94455458100378642"/>
+    <n v="-0.22972247103040749"/>
+    <n v="25.542025950437331"/>
+    <n v="0.92730289160598356"/>
+    <n v="25.542025950437331"/>
+    <n v="25.542025950437331"/>
+    <n v="0.92730289160598356"/>
+    <n v="438.67513980547648"/>
+    <n v="-0.2485467773809473"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="25.542025950437331"/>
+    <n v="0.92730289160598356"/>
+    <n v="25.542025950437331"/>
+    <n v="25.542025950437331"/>
+    <n v="0.92730289160598356"/>
+    <n v="438.67513980547648"/>
+    <n v="-0.2485467773809473"/>
+  </r>
+  <r>
+    <s v="16/04/2026 04:48:01"/>
+    <s v="04-16_04-48-01_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="7"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="4.2665844382620999E-2"/>
+    <n v="14.275541520505699"/>
+    <n v="0.95719910342343717"/>
+    <n v="-0.86998739325692354"/>
+    <n v="18.850041147916372"/>
+    <n v="0.9463494600146124"/>
+    <n v="18.850041147916372"/>
+    <n v="18.850041147916372"/>
+    <n v="0.9463494600146124"/>
+    <n v="643.83061484306597"/>
+    <n v="-0.83245542407066808"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="18.850041147916372"/>
+    <n v="0.9463494600146124"/>
+    <n v="18.850041147916372"/>
+    <n v="18.850041147916372"/>
+    <n v="0.9463494600146124"/>
+    <n v="643.83061484306597"/>
+    <n v="-0.83245542407066808"/>
+  </r>
+  <r>
+    <s v="16/04/2026 04:48:32"/>
+    <s v="04-16_04-48-32_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="8"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="5.0567721633465401E-2"/>
+    <n v="17.592795485020378"/>
+    <n v="0.94725332002534757"/>
+    <n v="-0.54362116488562262"/>
+    <n v="20.482780348111639"/>
+    <n v="0.94170239643218245"/>
+    <n v="20.482780348111639"/>
+    <n v="20.482780348111639"/>
+    <n v="0.94170239643218245"/>
+    <n v="524.0942034894714"/>
+    <n v="-0.49166449026716608"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="20.482780348111639"/>
+    <n v="0.94170239643218245"/>
+    <n v="20.482780348111639"/>
+    <n v="20.482780348111639"/>
+    <n v="0.94170239643218245"/>
+    <n v="524.0942034894714"/>
+    <n v="-0.49166449026716608"/>
+  </r>
+  <r>
+    <s v="16/04/2026 05:04:22"/>
+    <s v="04-16_05-04-22_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="9"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="5.5327297988010601E-2"/>
+    <n v="22.630352938106601"/>
+    <n v="0.93214972656527983"/>
+    <n v="-0.70482432609290857"/>
+    <n v="24.027946791284968"/>
+    <n v="0.93161222779425623"/>
+    <n v="24.027946791284968"/>
+    <n v="24.027946791284968"/>
+    <n v="0.93161222779425623"/>
+    <n v="566.71954488558868"/>
+    <n v="-0.61298372586023953"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="24.027946791284968"/>
+    <n v="0.93161222779425623"/>
+    <n v="24.027946791284968"/>
+    <n v="24.027946791284968"/>
+    <n v="0.93161222779425623"/>
+    <n v="566.71954488558868"/>
+    <n v="-0.61298372586023953"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{060B096D-A923-4002-95C4-7B64F2F15EA4}" name="TablaDinámica3" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:D9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80555896-D8D7-4966-94EA-A13C9398E88E}" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="F3:H7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="76">
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="11">
         <item x="0"/>
@@ -4930,14 +7474,15 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="0"/>
-        <item t="default" sd="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="7">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
@@ -4953,8 +7498,22 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item sd="0" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -5009,11 +7568,180 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <rowFields count="2">
-    <field x="7"/>
+  <rowFields count="3">
+    <field x="21"/>
+    <field x="22"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="7" item="3" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Promedio de global open R2" fld="43" subtotal="average" baseField="21" baseItem="0"/>
+    <dataField name="Promedio de global closed R2" fld="45" subtotal="average" baseField="21" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{060B096D-A923-4002-95C4-7B64F2F15EA4}" name="TablaDinámica3" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:D10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="76">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="0"/>
+        <item sd="0" x="5"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="7"/>
+    <field x="22"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="7">
     <i>
       <x/>
     </i>
@@ -5028,6 +7756,9 @@
     </i>
     <i>
       <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -5047,6 +7778,9 @@
       <x v="2"/>
     </i>
   </colItems>
+  <pageFields count="1">
+    <pageField fld="21" item="0" hier="-1"/>
+  </pageFields>
   <dataFields count="3">
     <dataField name="Promedio de global open R2" fld="43" subtotal="average" baseField="7" baseItem="0"/>
     <dataField name="Promedio de global closed R2" fld="45" subtotal="average" baseField="7" baseItem="0"/>
@@ -5065,8 +7799,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4004DF18-E8C7-4531-A991-D0FD7930891B}" name="Tabla1" displayName="Tabla1" ref="A1:BX51" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
-  <autoFilter ref="A1:BX51" xr:uid="{4004DF18-E8C7-4531-A991-D0FD7930891B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4004DF18-E8C7-4531-A991-D0FD7930891B}" name="Tabla1" displayName="Tabla1" ref="A1:BX81" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:BX81" xr:uid="{4004DF18-E8C7-4531-A991-D0FD7930891B}"/>
   <tableColumns count="76">
     <tableColumn id="1" xr3:uid="{1E4194BA-14DA-431A-A891-7358FCE9E2C7}" name="date"/>
     <tableColumn id="2" xr3:uid="{5FF0877E-1CE9-453D-A851-9AC28670B11D}" name="model_id"/>
@@ -5434,7 +8168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BX51"/>
+  <dimension ref="A1:BX81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.77734375" customWidth="1"/>
@@ -13933,6 +16667,4926 @@
         <v>-3.5266215766945019</v>
       </c>
     </row>
+    <row r="52" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>197</v>
+      </c>
+      <c r="B52" t="s">
+        <v>198</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52" t="s">
+        <v>78</v>
+      </c>
+      <c r="E52" t="s">
+        <v>79</v>
+      </c>
+      <c r="F52">
+        <v>16590</v>
+      </c>
+      <c r="G52">
+        <v>4.5</v>
+      </c>
+      <c r="H52" t="s">
+        <v>199</v>
+      </c>
+      <c r="I52" t="s">
+        <v>81</v>
+      </c>
+      <c r="J52">
+        <v>5</v>
+      </c>
+      <c r="K52">
+        <v>5</v>
+      </c>
+      <c r="L52" t="s">
+        <v>82</v>
+      </c>
+      <c r="M52" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" t="b">
+        <v>0</v>
+      </c>
+      <c r="O52" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>200</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52" t="s">
+        <v>85</v>
+      </c>
+      <c r="T52" t="s">
+        <v>86</v>
+      </c>
+      <c r="U52" t="s">
+        <v>87</v>
+      </c>
+      <c r="V52">
+        <v>1</v>
+      </c>
+      <c r="W52" t="s">
+        <v>201</v>
+      </c>
+      <c r="X52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z52">
+        <v>4000</v>
+      </c>
+      <c r="AA52">
+        <v>4000</v>
+      </c>
+      <c r="AC52">
+        <v>256</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE52">
+        <v>0.15</v>
+      </c>
+      <c r="AF52" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG52">
+        <v>40</v>
+      </c>
+      <c r="AH52">
+        <v>10</v>
+      </c>
+      <c r="AI52">
+        <v>30</v>
+      </c>
+      <c r="AJ52">
+        <v>5.7150730328352703E-2</v>
+      </c>
+      <c r="AK52">
+        <v>5.2629089424840103</v>
+      </c>
+      <c r="AL52">
+        <v>0.98422075820972799</v>
+      </c>
+      <c r="AM52">
+        <v>-3.6370012570852581</v>
+      </c>
+      <c r="AN52">
+        <v>8.1888289403937069</v>
+      </c>
+      <c r="AO52">
+        <v>0.97669314931184359</v>
+      </c>
+      <c r="AP52">
+        <v>8.1888289403937069</v>
+      </c>
+      <c r="AQ52">
+        <v>8.1888289403937069</v>
+      </c>
+      <c r="AR52">
+        <v>0.97669314931184359</v>
+      </c>
+      <c r="AS52">
+        <v>1570.8733875388079</v>
+      </c>
+      <c r="AT52">
+        <v>-3.4709825739265319</v>
+      </c>
+      <c r="AU52">
+        <v>0.2</v>
+      </c>
+      <c r="AV52" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR52">
+        <v>8.1888289403937069</v>
+      </c>
+      <c r="BS52">
+        <v>0.97669314931184359</v>
+      </c>
+      <c r="BT52">
+        <v>8.1888289403937069</v>
+      </c>
+      <c r="BU52">
+        <v>8.1888289403937069</v>
+      </c>
+      <c r="BV52">
+        <v>0.97669314931184359</v>
+      </c>
+      <c r="BW52">
+        <v>1570.8733875388079</v>
+      </c>
+      <c r="BX52">
+        <v>-3.4709825739265319</v>
+      </c>
+    </row>
+    <row r="53" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>202</v>
+      </c>
+      <c r="B53" t="s">
+        <v>203</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53" t="s">
+        <v>78</v>
+      </c>
+      <c r="E53" t="s">
+        <v>79</v>
+      </c>
+      <c r="F53">
+        <v>16590</v>
+      </c>
+      <c r="G53">
+        <v>4.5</v>
+      </c>
+      <c r="H53" t="s">
+        <v>199</v>
+      </c>
+      <c r="I53" t="s">
+        <v>81</v>
+      </c>
+      <c r="J53">
+        <v>5</v>
+      </c>
+      <c r="K53">
+        <v>5</v>
+      </c>
+      <c r="L53" t="s">
+        <v>82</v>
+      </c>
+      <c r="M53" t="b">
+        <v>1</v>
+      </c>
+      <c r="N53" t="b">
+        <v>0</v>
+      </c>
+      <c r="O53" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>200</v>
+      </c>
+      <c r="R53">
+        <v>1</v>
+      </c>
+      <c r="S53" t="s">
+        <v>85</v>
+      </c>
+      <c r="T53" t="s">
+        <v>86</v>
+      </c>
+      <c r="U53" t="s">
+        <v>87</v>
+      </c>
+      <c r="V53">
+        <v>1</v>
+      </c>
+      <c r="W53" t="s">
+        <v>201</v>
+      </c>
+      <c r="X53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z53">
+        <v>4000</v>
+      </c>
+      <c r="AA53">
+        <v>4000</v>
+      </c>
+      <c r="AC53">
+        <v>256</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE53">
+        <v>0.15</v>
+      </c>
+      <c r="AF53" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG53">
+        <v>40</v>
+      </c>
+      <c r="AH53">
+        <v>10</v>
+      </c>
+      <c r="AI53">
+        <v>30</v>
+      </c>
+      <c r="AJ53">
+        <v>7.4276302489280605E-2</v>
+      </c>
+      <c r="AK53">
+        <v>5.32380974050532</v>
+      </c>
+      <c r="AL53">
+        <v>0.9840381655736592</v>
+      </c>
+      <c r="AM53">
+        <v>-3.8512886290860249</v>
+      </c>
+      <c r="AN53">
+        <v>8.0535178159390473</v>
+      </c>
+      <c r="AO53">
+        <v>0.97707826862463742</v>
+      </c>
+      <c r="AP53">
+        <v>8.0535178159390473</v>
+      </c>
+      <c r="AQ53">
+        <v>8.0535178159390473</v>
+      </c>
+      <c r="AR53">
+        <v>0.97707826862463742</v>
+      </c>
+      <c r="AS53">
+        <v>1637.0723537957961</v>
+      </c>
+      <c r="AT53">
+        <v>-3.6593965014236862</v>
+      </c>
+      <c r="AU53">
+        <v>0.2</v>
+      </c>
+      <c r="AV53" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR53">
+        <v>8.0535178159390473</v>
+      </c>
+      <c r="BS53">
+        <v>0.97707826862463742</v>
+      </c>
+      <c r="BT53">
+        <v>8.0535178159390473</v>
+      </c>
+      <c r="BU53">
+        <v>8.0535178159390473</v>
+      </c>
+      <c r="BV53">
+        <v>0.97707826862463742</v>
+      </c>
+      <c r="BW53">
+        <v>1637.0723537957961</v>
+      </c>
+      <c r="BX53">
+        <v>-3.6593965014236862</v>
+      </c>
+    </row>
+    <row r="54" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>204</v>
+      </c>
+      <c r="B54" t="s">
+        <v>205</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54" t="s">
+        <v>97</v>
+      </c>
+      <c r="E54" t="s">
+        <v>79</v>
+      </c>
+      <c r="F54">
+        <v>16590</v>
+      </c>
+      <c r="G54">
+        <v>4.5</v>
+      </c>
+      <c r="H54" t="s">
+        <v>199</v>
+      </c>
+      <c r="I54" t="s">
+        <v>81</v>
+      </c>
+      <c r="J54">
+        <v>5</v>
+      </c>
+      <c r="K54">
+        <v>5</v>
+      </c>
+      <c r="L54" t="s">
+        <v>82</v>
+      </c>
+      <c r="M54" t="b">
+        <v>1</v>
+      </c>
+      <c r="N54" t="b">
+        <v>0</v>
+      </c>
+      <c r="O54" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>200</v>
+      </c>
+      <c r="R54">
+        <v>1</v>
+      </c>
+      <c r="S54" t="s">
+        <v>85</v>
+      </c>
+      <c r="T54" t="s">
+        <v>86</v>
+      </c>
+      <c r="U54" t="s">
+        <v>87</v>
+      </c>
+      <c r="V54">
+        <v>1</v>
+      </c>
+      <c r="W54" t="s">
+        <v>201</v>
+      </c>
+      <c r="X54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z54">
+        <v>4000</v>
+      </c>
+      <c r="AA54">
+        <v>4000</v>
+      </c>
+      <c r="AC54">
+        <v>256</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE54">
+        <v>0.15</v>
+      </c>
+      <c r="AF54" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG54">
+        <v>40</v>
+      </c>
+      <c r="AH54">
+        <v>10</v>
+      </c>
+      <c r="AI54">
+        <v>30</v>
+      </c>
+      <c r="AJ54">
+        <v>5.1604037359194797E-2</v>
+      </c>
+      <c r="AK54">
+        <v>4.9834633784533731</v>
+      </c>
+      <c r="AL54">
+        <v>0.98505859127320061</v>
+      </c>
+      <c r="AM54">
+        <v>-3.7548451378461132</v>
+      </c>
+      <c r="AN54">
+        <v>7.716047078567998</v>
+      </c>
+      <c r="AO54">
+        <v>0.97803876983241478</v>
+      </c>
+      <c r="AP54">
+        <v>7.716047078567998</v>
+      </c>
+      <c r="AQ54">
+        <v>7.716047078567998</v>
+      </c>
+      <c r="AR54">
+        <v>0.97803876983241478</v>
+      </c>
+      <c r="AS54">
+        <v>1609.0161075963031</v>
+      </c>
+      <c r="AT54">
+        <v>-3.5795434789950238</v>
+      </c>
+      <c r="AU54">
+        <v>0.2</v>
+      </c>
+      <c r="AV54" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR54">
+        <v>7.716047078567998</v>
+      </c>
+      <c r="BS54">
+        <v>0.97803876983241478</v>
+      </c>
+      <c r="BT54">
+        <v>7.716047078567998</v>
+      </c>
+      <c r="BU54">
+        <v>7.716047078567998</v>
+      </c>
+      <c r="BV54">
+        <v>0.97803876983241478</v>
+      </c>
+      <c r="BW54">
+        <v>1609.0161075963031</v>
+      </c>
+      <c r="BX54">
+        <v>-3.5795434789950238</v>
+      </c>
+    </row>
+    <row r="55" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>206</v>
+      </c>
+      <c r="B55" t="s">
+        <v>207</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55" t="s">
+        <v>78</v>
+      </c>
+      <c r="E55" t="s">
+        <v>79</v>
+      </c>
+      <c r="F55">
+        <v>16590</v>
+      </c>
+      <c r="G55">
+        <v>4.5</v>
+      </c>
+      <c r="H55" t="s">
+        <v>199</v>
+      </c>
+      <c r="I55" t="s">
+        <v>81</v>
+      </c>
+      <c r="J55">
+        <v>5</v>
+      </c>
+      <c r="K55">
+        <v>5</v>
+      </c>
+      <c r="L55" t="s">
+        <v>82</v>
+      </c>
+      <c r="M55" t="b">
+        <v>1</v>
+      </c>
+      <c r="N55" t="b">
+        <v>0</v>
+      </c>
+      <c r="O55" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>200</v>
+      </c>
+      <c r="R55">
+        <v>1</v>
+      </c>
+      <c r="S55" t="s">
+        <v>85</v>
+      </c>
+      <c r="T55" t="s">
+        <v>86</v>
+      </c>
+      <c r="U55" t="s">
+        <v>87</v>
+      </c>
+      <c r="V55">
+        <v>1</v>
+      </c>
+      <c r="W55" t="s">
+        <v>201</v>
+      </c>
+      <c r="X55" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z55">
+        <v>4000</v>
+      </c>
+      <c r="AA55">
+        <v>4000</v>
+      </c>
+      <c r="AC55">
+        <v>256</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE55">
+        <v>0.15</v>
+      </c>
+      <c r="AF55" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG55">
+        <v>40</v>
+      </c>
+      <c r="AH55">
+        <v>10</v>
+      </c>
+      <c r="AI55">
+        <v>30</v>
+      </c>
+      <c r="AJ55">
+        <v>5.1529209445481998E-2</v>
+      </c>
+      <c r="AK55">
+        <v>5.6807518930531371</v>
+      </c>
+      <c r="AL55">
+        <v>0.98296798241226602</v>
+      </c>
+      <c r="AM55">
+        <v>-3.6395890215677742</v>
+      </c>
+      <c r="AN55">
+        <v>8.3530439583657721</v>
+      </c>
+      <c r="AO55">
+        <v>0.97622576442293119</v>
+      </c>
+      <c r="AP55">
+        <v>8.3530439583657721</v>
+      </c>
+      <c r="AQ55">
+        <v>8.3530439583657721</v>
+      </c>
+      <c r="AR55">
+        <v>0.97622576442293119</v>
+      </c>
+      <c r="AS55">
+        <v>1571.459982038853</v>
+      </c>
+      <c r="AT55">
+        <v>-3.4726521252783278</v>
+      </c>
+      <c r="AU55">
+        <v>0.2</v>
+      </c>
+      <c r="AV55" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR55">
+        <v>8.3530439583657721</v>
+      </c>
+      <c r="BS55">
+        <v>0.97622576442293119</v>
+      </c>
+      <c r="BT55">
+        <v>8.3530439583657721</v>
+      </c>
+      <c r="BU55">
+        <v>8.3530439583657721</v>
+      </c>
+      <c r="BV55">
+        <v>0.97622576442293119</v>
+      </c>
+      <c r="BW55">
+        <v>1571.459982038853</v>
+      </c>
+      <c r="BX55">
+        <v>-3.4726521252783278</v>
+      </c>
+    </row>
+    <row r="56" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>208</v>
+      </c>
+      <c r="B56" t="s">
+        <v>209</v>
+      </c>
+      <c r="C56">
+        <v>4</v>
+      </c>
+      <c r="D56" t="s">
+        <v>78</v>
+      </c>
+      <c r="E56" t="s">
+        <v>79</v>
+      </c>
+      <c r="F56">
+        <v>16590</v>
+      </c>
+      <c r="G56">
+        <v>4.5</v>
+      </c>
+      <c r="H56" t="s">
+        <v>199</v>
+      </c>
+      <c r="I56" t="s">
+        <v>81</v>
+      </c>
+      <c r="J56">
+        <v>5</v>
+      </c>
+      <c r="K56">
+        <v>5</v>
+      </c>
+      <c r="L56" t="s">
+        <v>82</v>
+      </c>
+      <c r="M56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N56" t="b">
+        <v>0</v>
+      </c>
+      <c r="O56" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>200</v>
+      </c>
+      <c r="R56">
+        <v>1</v>
+      </c>
+      <c r="S56" t="s">
+        <v>85</v>
+      </c>
+      <c r="T56" t="s">
+        <v>86</v>
+      </c>
+      <c r="U56" t="s">
+        <v>87</v>
+      </c>
+      <c r="V56">
+        <v>1</v>
+      </c>
+      <c r="W56" t="s">
+        <v>201</v>
+      </c>
+      <c r="X56" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z56">
+        <v>4000</v>
+      </c>
+      <c r="AA56">
+        <v>4000</v>
+      </c>
+      <c r="AC56">
+        <v>256</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE56">
+        <v>0.15</v>
+      </c>
+      <c r="AF56" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG56">
+        <v>40</v>
+      </c>
+      <c r="AH56">
+        <v>10</v>
+      </c>
+      <c r="AI56">
+        <v>30</v>
+      </c>
+      <c r="AJ56">
+        <v>3.2361351023914103E-2</v>
+      </c>
+      <c r="AK56">
+        <v>6.1346238380219011</v>
+      </c>
+      <c r="AL56">
+        <v>0.98160718456458318</v>
+      </c>
+      <c r="AM56">
+        <v>-3.804297484629116</v>
+      </c>
+      <c r="AN56">
+        <v>9.2016147239691684</v>
+      </c>
+      <c r="AO56">
+        <v>0.97381058243827723</v>
+      </c>
+      <c r="AP56">
+        <v>9.2016147239691684</v>
+      </c>
+      <c r="AQ56">
+        <v>9.2016147239691684</v>
+      </c>
+      <c r="AR56">
+        <v>0.97381058243827723</v>
+      </c>
+      <c r="AS56">
+        <v>1624.5102171318081</v>
+      </c>
+      <c r="AT56">
+        <v>-3.623642446029081</v>
+      </c>
+      <c r="AU56">
+        <v>0.2</v>
+      </c>
+      <c r="AV56" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR56">
+        <v>9.2016147239691684</v>
+      </c>
+      <c r="BS56">
+        <v>0.97381058243827723</v>
+      </c>
+      <c r="BT56">
+        <v>9.2016147239691684</v>
+      </c>
+      <c r="BU56">
+        <v>9.2016147239691684</v>
+      </c>
+      <c r="BV56">
+        <v>0.97381058243827723</v>
+      </c>
+      <c r="BW56">
+        <v>1624.5102171318081</v>
+      </c>
+      <c r="BX56">
+        <v>-3.623642446029081</v>
+      </c>
+    </row>
+    <row r="57" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>210</v>
+      </c>
+      <c r="B57" t="s">
+        <v>211</v>
+      </c>
+      <c r="C57">
+        <v>5</v>
+      </c>
+      <c r="D57" t="s">
+        <v>78</v>
+      </c>
+      <c r="E57" t="s">
+        <v>79</v>
+      </c>
+      <c r="F57">
+        <v>16590</v>
+      </c>
+      <c r="G57">
+        <v>4.5</v>
+      </c>
+      <c r="H57" t="s">
+        <v>199</v>
+      </c>
+      <c r="I57" t="s">
+        <v>81</v>
+      </c>
+      <c r="J57">
+        <v>5</v>
+      </c>
+      <c r="K57">
+        <v>5</v>
+      </c>
+      <c r="L57" t="s">
+        <v>82</v>
+      </c>
+      <c r="M57" t="b">
+        <v>1</v>
+      </c>
+      <c r="N57" t="b">
+        <v>0</v>
+      </c>
+      <c r="O57" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>200</v>
+      </c>
+      <c r="R57">
+        <v>1</v>
+      </c>
+      <c r="S57" t="s">
+        <v>85</v>
+      </c>
+      <c r="T57" t="s">
+        <v>86</v>
+      </c>
+      <c r="U57" t="s">
+        <v>87</v>
+      </c>
+      <c r="V57">
+        <v>1</v>
+      </c>
+      <c r="W57" t="s">
+        <v>201</v>
+      </c>
+      <c r="X57" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z57">
+        <v>4000</v>
+      </c>
+      <c r="AA57">
+        <v>4000</v>
+      </c>
+      <c r="AC57">
+        <v>256</v>
+      </c>
+      <c r="AD57" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE57">
+        <v>0.15</v>
+      </c>
+      <c r="AF57" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG57">
+        <v>40</v>
+      </c>
+      <c r="AH57">
+        <v>10</v>
+      </c>
+      <c r="AI57">
+        <v>30</v>
+      </c>
+      <c r="AJ57">
+        <v>7.2798951399546494E-2</v>
+      </c>
+      <c r="AK57">
+        <v>5.33760499111815</v>
+      </c>
+      <c r="AL57">
+        <v>0.98399680468420503</v>
+      </c>
+      <c r="AM57">
+        <v>-3.667662959479729</v>
+      </c>
+      <c r="AN57">
+        <v>8.2460592780144673</v>
+      </c>
+      <c r="AO57">
+        <v>0.97653026168243162</v>
+      </c>
+      <c r="AP57">
+        <v>8.2460592780144673</v>
+      </c>
+      <c r="AQ57">
+        <v>8.2460592780144673</v>
+      </c>
+      <c r="AR57">
+        <v>0.97653026168243162</v>
+      </c>
+      <c r="AS57">
+        <v>1582.088118269746</v>
+      </c>
+      <c r="AT57">
+        <v>-3.502901674515448</v>
+      </c>
+      <c r="AU57">
+        <v>0.2</v>
+      </c>
+      <c r="AV57" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR57">
+        <v>8.2460592780144673</v>
+      </c>
+      <c r="BS57">
+        <v>0.97653026168243162</v>
+      </c>
+      <c r="BT57">
+        <v>8.2460592780144673</v>
+      </c>
+      <c r="BU57">
+        <v>8.2460592780144673</v>
+      </c>
+      <c r="BV57">
+        <v>0.97653026168243162</v>
+      </c>
+      <c r="BW57">
+        <v>1582.088118269746</v>
+      </c>
+      <c r="BX57">
+        <v>-3.502901674515448</v>
+      </c>
+    </row>
+    <row r="58" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>212</v>
+      </c>
+      <c r="B58" t="s">
+        <v>213</v>
+      </c>
+      <c r="C58">
+        <v>6</v>
+      </c>
+      <c r="D58" t="s">
+        <v>78</v>
+      </c>
+      <c r="E58" t="s">
+        <v>79</v>
+      </c>
+      <c r="F58">
+        <v>16590</v>
+      </c>
+      <c r="G58">
+        <v>4.5</v>
+      </c>
+      <c r="H58" t="s">
+        <v>199</v>
+      </c>
+      <c r="I58" t="s">
+        <v>81</v>
+      </c>
+      <c r="J58">
+        <v>5</v>
+      </c>
+      <c r="K58">
+        <v>5</v>
+      </c>
+      <c r="L58" t="s">
+        <v>82</v>
+      </c>
+      <c r="M58" t="b">
+        <v>1</v>
+      </c>
+      <c r="N58" t="b">
+        <v>0</v>
+      </c>
+      <c r="O58" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>200</v>
+      </c>
+      <c r="R58">
+        <v>1</v>
+      </c>
+      <c r="S58" t="s">
+        <v>85</v>
+      </c>
+      <c r="T58" t="s">
+        <v>86</v>
+      </c>
+      <c r="U58" t="s">
+        <v>87</v>
+      </c>
+      <c r="V58">
+        <v>1</v>
+      </c>
+      <c r="W58" t="s">
+        <v>201</v>
+      </c>
+      <c r="X58" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z58">
+        <v>4000</v>
+      </c>
+      <c r="AA58">
+        <v>4000</v>
+      </c>
+      <c r="AC58">
+        <v>256</v>
+      </c>
+      <c r="AD58" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE58">
+        <v>0.15</v>
+      </c>
+      <c r="AF58" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG58">
+        <v>40</v>
+      </c>
+      <c r="AH58">
+        <v>10</v>
+      </c>
+      <c r="AI58">
+        <v>30</v>
+      </c>
+      <c r="AJ58">
+        <v>5.3524819002593302E-2</v>
+      </c>
+      <c r="AK58">
+        <v>6.4125991309808636</v>
+      </c>
+      <c r="AL58">
+        <v>0.98077375966454095</v>
+      </c>
+      <c r="AM58">
+        <v>-3.315272679274432</v>
+      </c>
+      <c r="AN58">
+        <v>10.240591082057311</v>
+      </c>
+      <c r="AO58">
+        <v>0.97085347257278265</v>
+      </c>
+      <c r="AP58">
+        <v>10.240591082057311</v>
+      </c>
+      <c r="AQ58">
+        <v>10.240591082057311</v>
+      </c>
+      <c r="AR58">
+        <v>0.97085347257278265</v>
+      </c>
+      <c r="AS58">
+        <v>1471.6420377514889</v>
+      </c>
+      <c r="AT58">
+        <v>-3.188552659965469</v>
+      </c>
+      <c r="AU58">
+        <v>0.2</v>
+      </c>
+      <c r="AV58" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR58">
+        <v>10.240591082057311</v>
+      </c>
+      <c r="BS58">
+        <v>0.97085347257278265</v>
+      </c>
+      <c r="BT58">
+        <v>10.240591082057311</v>
+      </c>
+      <c r="BU58">
+        <v>10.240591082057311</v>
+      </c>
+      <c r="BV58">
+        <v>0.97085347257278265</v>
+      </c>
+      <c r="BW58">
+        <v>1471.6420377514889</v>
+      </c>
+      <c r="BX58">
+        <v>-3.188552659965469</v>
+      </c>
+    </row>
+    <row r="59" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>214</v>
+      </c>
+      <c r="B59" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59">
+        <v>7</v>
+      </c>
+      <c r="D59" t="s">
+        <v>97</v>
+      </c>
+      <c r="E59" t="s">
+        <v>79</v>
+      </c>
+      <c r="F59">
+        <v>16590</v>
+      </c>
+      <c r="G59">
+        <v>4.5</v>
+      </c>
+      <c r="H59" t="s">
+        <v>199</v>
+      </c>
+      <c r="I59" t="s">
+        <v>81</v>
+      </c>
+      <c r="J59">
+        <v>5</v>
+      </c>
+      <c r="K59">
+        <v>5</v>
+      </c>
+      <c r="L59" t="s">
+        <v>82</v>
+      </c>
+      <c r="M59" t="b">
+        <v>1</v>
+      </c>
+      <c r="N59" t="b">
+        <v>0</v>
+      </c>
+      <c r="O59" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>200</v>
+      </c>
+      <c r="R59">
+        <v>1</v>
+      </c>
+      <c r="S59" t="s">
+        <v>85</v>
+      </c>
+      <c r="T59" t="s">
+        <v>86</v>
+      </c>
+      <c r="U59" t="s">
+        <v>87</v>
+      </c>
+      <c r="V59">
+        <v>1</v>
+      </c>
+      <c r="W59" t="s">
+        <v>201</v>
+      </c>
+      <c r="X59" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z59">
+        <v>4000</v>
+      </c>
+      <c r="AA59">
+        <v>4000</v>
+      </c>
+      <c r="AC59">
+        <v>256</v>
+      </c>
+      <c r="AD59" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE59">
+        <v>0.15</v>
+      </c>
+      <c r="AF59" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG59">
+        <v>40</v>
+      </c>
+      <c r="AH59">
+        <v>10</v>
+      </c>
+      <c r="AI59">
+        <v>30</v>
+      </c>
+      <c r="AJ59">
+        <v>5.5301536648489497E-2</v>
+      </c>
+      <c r="AK59">
+        <v>5.3794103542524301</v>
+      </c>
+      <c r="AL59">
+        <v>0.98387146393819658</v>
+      </c>
+      <c r="AM59">
+        <v>-3.7503506951755821</v>
+      </c>
+      <c r="AN59">
+        <v>8.2290284715517448</v>
+      </c>
+      <c r="AO59">
+        <v>0.97657873435980902</v>
+      </c>
+      <c r="AP59">
+        <v>8.2290284715517448</v>
+      </c>
+      <c r="AQ59">
+        <v>8.2290284715517448</v>
+      </c>
+      <c r="AR59">
+        <v>0.97657873435980902</v>
+      </c>
+      <c r="AS59">
+        <v>1607.6479781961821</v>
+      </c>
+      <c r="AT59">
+        <v>-3.5756495415489238</v>
+      </c>
+      <c r="AU59">
+        <v>0.2</v>
+      </c>
+      <c r="AV59" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR59">
+        <v>8.2290284715517448</v>
+      </c>
+      <c r="BS59">
+        <v>0.97657873435980902</v>
+      </c>
+      <c r="BT59">
+        <v>8.2290284715517448</v>
+      </c>
+      <c r="BU59">
+        <v>8.2290284715517448</v>
+      </c>
+      <c r="BV59">
+        <v>0.97657873435980902</v>
+      </c>
+      <c r="BW59">
+        <v>1607.6479781961821</v>
+      </c>
+      <c r="BX59">
+        <v>-3.5756495415489238</v>
+      </c>
+    </row>
+    <row r="60" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>216</v>
+      </c>
+      <c r="B60" t="s">
+        <v>217</v>
+      </c>
+      <c r="C60">
+        <v>8</v>
+      </c>
+      <c r="D60" t="s">
+        <v>78</v>
+      </c>
+      <c r="E60" t="s">
+        <v>79</v>
+      </c>
+      <c r="F60">
+        <v>16590</v>
+      </c>
+      <c r="G60">
+        <v>4.5</v>
+      </c>
+      <c r="H60" t="s">
+        <v>199</v>
+      </c>
+      <c r="I60" t="s">
+        <v>81</v>
+      </c>
+      <c r="J60">
+        <v>5</v>
+      </c>
+      <c r="K60">
+        <v>5</v>
+      </c>
+      <c r="L60" t="s">
+        <v>82</v>
+      </c>
+      <c r="M60" t="b">
+        <v>1</v>
+      </c>
+      <c r="N60" t="b">
+        <v>0</v>
+      </c>
+      <c r="O60" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>200</v>
+      </c>
+      <c r="R60">
+        <v>1</v>
+      </c>
+      <c r="S60" t="s">
+        <v>85</v>
+      </c>
+      <c r="T60" t="s">
+        <v>86</v>
+      </c>
+      <c r="U60" t="s">
+        <v>87</v>
+      </c>
+      <c r="V60">
+        <v>1</v>
+      </c>
+      <c r="W60" t="s">
+        <v>201</v>
+      </c>
+      <c r="X60" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z60">
+        <v>4000</v>
+      </c>
+      <c r="AA60">
+        <v>4000</v>
+      </c>
+      <c r="AC60">
+        <v>256</v>
+      </c>
+      <c r="AD60" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE60">
+        <v>0.15</v>
+      </c>
+      <c r="AF60" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG60">
+        <v>40</v>
+      </c>
+      <c r="AH60">
+        <v>10</v>
+      </c>
+      <c r="AI60">
+        <v>30</v>
+      </c>
+      <c r="AJ60">
+        <v>5.5489815718812903E-2</v>
+      </c>
+      <c r="AK60">
+        <v>5.4546171420801723</v>
+      </c>
+      <c r="AL60">
+        <v>0.98364597911556839</v>
+      </c>
+      <c r="AM60">
+        <v>-3.6406276373494229</v>
+      </c>
+      <c r="AN60">
+        <v>8.2006302906341073</v>
+      </c>
+      <c r="AO60">
+        <v>0.97665956058872161</v>
+      </c>
+      <c r="AP60">
+        <v>8.2006302906341073</v>
+      </c>
+      <c r="AQ60">
+        <v>8.2006302906341073</v>
+      </c>
+      <c r="AR60">
+        <v>0.97665956058872161</v>
+      </c>
+      <c r="AS60">
+        <v>1577.740266855822</v>
+      </c>
+      <c r="AT60">
+        <v>-3.490526922953749</v>
+      </c>
+      <c r="AU60">
+        <v>0.2</v>
+      </c>
+      <c r="AV60" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR60">
+        <v>8.2006302906341073</v>
+      </c>
+      <c r="BS60">
+        <v>0.97665956058872161</v>
+      </c>
+      <c r="BT60">
+        <v>8.2006302906341073</v>
+      </c>
+      <c r="BU60">
+        <v>8.2006302906341073</v>
+      </c>
+      <c r="BV60">
+        <v>0.97665956058872161</v>
+      </c>
+      <c r="BW60">
+        <v>1577.740266855822</v>
+      </c>
+      <c r="BX60">
+        <v>-3.490526922953749</v>
+      </c>
+    </row>
+    <row r="61" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>218</v>
+      </c>
+      <c r="B61" t="s">
+        <v>219</v>
+      </c>
+      <c r="C61">
+        <v>9</v>
+      </c>
+      <c r="D61" t="s">
+        <v>97</v>
+      </c>
+      <c r="E61" t="s">
+        <v>79</v>
+      </c>
+      <c r="F61">
+        <v>16590</v>
+      </c>
+      <c r="G61">
+        <v>4.5</v>
+      </c>
+      <c r="H61" t="s">
+        <v>199</v>
+      </c>
+      <c r="I61" t="s">
+        <v>81</v>
+      </c>
+      <c r="J61">
+        <v>5</v>
+      </c>
+      <c r="K61">
+        <v>5</v>
+      </c>
+      <c r="L61" t="s">
+        <v>82</v>
+      </c>
+      <c r="M61" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" t="b">
+        <v>0</v>
+      </c>
+      <c r="O61" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>200</v>
+      </c>
+      <c r="R61">
+        <v>1</v>
+      </c>
+      <c r="S61" t="s">
+        <v>85</v>
+      </c>
+      <c r="T61" t="s">
+        <v>86</v>
+      </c>
+      <c r="U61" t="s">
+        <v>87</v>
+      </c>
+      <c r="V61">
+        <v>1</v>
+      </c>
+      <c r="W61" t="s">
+        <v>201</v>
+      </c>
+      <c r="X61" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z61">
+        <v>4000</v>
+      </c>
+      <c r="AA61">
+        <v>4000</v>
+      </c>
+      <c r="AC61">
+        <v>256</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE61">
+        <v>0.15</v>
+      </c>
+      <c r="AF61" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG61">
+        <v>40</v>
+      </c>
+      <c r="AH61">
+        <v>10</v>
+      </c>
+      <c r="AI61">
+        <v>30</v>
+      </c>
+      <c r="AJ61">
+        <v>4.5530792681009201E-2</v>
+      </c>
+      <c r="AK61">
+        <v>5.1988481378496738</v>
+      </c>
+      <c r="AL61">
+        <v>0.98441282517053841</v>
+      </c>
+      <c r="AM61">
+        <v>-3.705521951131427</v>
+      </c>
+      <c r="AN61">
+        <v>7.8935863878005126</v>
+      </c>
+      <c r="AO61">
+        <v>0.97753346166177402</v>
+      </c>
+      <c r="AP61">
+        <v>7.8935863878005126</v>
+      </c>
+      <c r="AQ61">
+        <v>7.8935863878005126</v>
+      </c>
+      <c r="AR61">
+        <v>0.97753346166177402</v>
+      </c>
+      <c r="AS61">
+        <v>1591.074277294965</v>
+      </c>
+      <c r="AT61">
+        <v>-3.528477867178077</v>
+      </c>
+      <c r="AU61">
+        <v>0.2</v>
+      </c>
+      <c r="AV61" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR61">
+        <v>7.8935863878005126</v>
+      </c>
+      <c r="BS61">
+        <v>0.97753346166177402</v>
+      </c>
+      <c r="BT61">
+        <v>7.8935863878005126</v>
+      </c>
+      <c r="BU61">
+        <v>7.8935863878005126</v>
+      </c>
+      <c r="BV61">
+        <v>0.97753346166177402</v>
+      </c>
+      <c r="BW61">
+        <v>1591.074277294965</v>
+      </c>
+      <c r="BX61">
+        <v>-3.528477867178077</v>
+      </c>
+    </row>
+    <row r="62" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>220</v>
+      </c>
+      <c r="B62" t="s">
+        <v>221</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62" t="s">
+        <v>78</v>
+      </c>
+      <c r="E62" t="s">
+        <v>79</v>
+      </c>
+      <c r="F62">
+        <v>16590</v>
+      </c>
+      <c r="G62">
+        <v>4.5</v>
+      </c>
+      <c r="H62" t="s">
+        <v>199</v>
+      </c>
+      <c r="I62" t="s">
+        <v>81</v>
+      </c>
+      <c r="J62">
+        <v>5</v>
+      </c>
+      <c r="K62">
+        <v>5</v>
+      </c>
+      <c r="L62" t="s">
+        <v>82</v>
+      </c>
+      <c r="M62" t="b">
+        <v>1</v>
+      </c>
+      <c r="N62" t="b">
+        <v>0</v>
+      </c>
+      <c r="O62" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>222</v>
+      </c>
+      <c r="R62">
+        <v>1</v>
+      </c>
+      <c r="S62" t="s">
+        <v>85</v>
+      </c>
+      <c r="T62" t="s">
+        <v>86</v>
+      </c>
+      <c r="U62" t="s">
+        <v>87</v>
+      </c>
+      <c r="V62">
+        <v>3</v>
+      </c>
+      <c r="W62" t="s">
+        <v>201</v>
+      </c>
+      <c r="X62" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z62">
+        <v>4000</v>
+      </c>
+      <c r="AA62">
+        <v>4000</v>
+      </c>
+      <c r="AC62">
+        <v>256</v>
+      </c>
+      <c r="AD62" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE62">
+        <v>0.15</v>
+      </c>
+      <c r="AF62" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG62">
+        <v>60</v>
+      </c>
+      <c r="AH62">
+        <v>30</v>
+      </c>
+      <c r="AI62">
+        <v>30</v>
+      </c>
+      <c r="AJ62">
+        <v>4.3384309475530902E-2</v>
+      </c>
+      <c r="AK62">
+        <v>7.2689830642188591</v>
+      </c>
+      <c r="AL62">
+        <v>0.97820615127618682</v>
+      </c>
+      <c r="AM62">
+        <v>-0.52769369452162795</v>
+      </c>
+      <c r="AN62">
+        <v>10.934054881481099</v>
+      </c>
+      <c r="AO62">
+        <v>0.9688797523560756</v>
+      </c>
+      <c r="AP62">
+        <v>10.934054881481099</v>
+      </c>
+      <c r="AQ62">
+        <v>10.934054881481099</v>
+      </c>
+      <c r="AR62">
+        <v>0.9688797523560756</v>
+      </c>
+      <c r="AS62">
+        <v>542.37491525372229</v>
+      </c>
+      <c r="AT62">
+        <v>-0.54369461846546474</v>
+      </c>
+      <c r="AU62">
+        <v>0.2</v>
+      </c>
+      <c r="AV62" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR62">
+        <v>10.934054881481099</v>
+      </c>
+      <c r="BS62">
+        <v>0.9688797523560756</v>
+      </c>
+      <c r="BT62">
+        <v>10.934054881481099</v>
+      </c>
+      <c r="BU62">
+        <v>10.934054881481099</v>
+      </c>
+      <c r="BV62">
+        <v>0.9688797523560756</v>
+      </c>
+      <c r="BW62">
+        <v>542.37491525372229</v>
+      </c>
+      <c r="BX62">
+        <v>-0.54369461846546474</v>
+      </c>
+    </row>
+    <row r="63" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>223</v>
+      </c>
+      <c r="B63" t="s">
+        <v>224</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63" t="s">
+        <v>97</v>
+      </c>
+      <c r="E63" t="s">
+        <v>79</v>
+      </c>
+      <c r="F63">
+        <v>16590</v>
+      </c>
+      <c r="G63">
+        <v>4.5</v>
+      </c>
+      <c r="H63" t="s">
+        <v>199</v>
+      </c>
+      <c r="I63" t="s">
+        <v>81</v>
+      </c>
+      <c r="J63">
+        <v>5</v>
+      </c>
+      <c r="K63">
+        <v>5</v>
+      </c>
+      <c r="L63" t="s">
+        <v>82</v>
+      </c>
+      <c r="M63" t="b">
+        <v>1</v>
+      </c>
+      <c r="N63" t="b">
+        <v>0</v>
+      </c>
+      <c r="O63" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>222</v>
+      </c>
+      <c r="R63">
+        <v>1</v>
+      </c>
+      <c r="S63" t="s">
+        <v>85</v>
+      </c>
+      <c r="T63" t="s">
+        <v>86</v>
+      </c>
+      <c r="U63" t="s">
+        <v>87</v>
+      </c>
+      <c r="V63">
+        <v>3</v>
+      </c>
+      <c r="W63" t="s">
+        <v>201</v>
+      </c>
+      <c r="X63" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z63">
+        <v>4000</v>
+      </c>
+      <c r="AA63">
+        <v>4000</v>
+      </c>
+      <c r="AC63">
+        <v>256</v>
+      </c>
+      <c r="AD63" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE63">
+        <v>0.15</v>
+      </c>
+      <c r="AF63" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG63">
+        <v>60</v>
+      </c>
+      <c r="AH63">
+        <v>30</v>
+      </c>
+      <c r="AI63">
+        <v>30</v>
+      </c>
+      <c r="AJ63">
+        <v>4.7437990433947502E-2</v>
+      </c>
+      <c r="AK63">
+        <v>8.5839315542630299</v>
+      </c>
+      <c r="AL63">
+        <v>0.97426367566186101</v>
+      </c>
+      <c r="AM63">
+        <v>-0.57480940575505923</v>
+      </c>
+      <c r="AN63">
+        <v>15.449850579664741</v>
+      </c>
+      <c r="AO63">
+        <v>0.9560270017562168</v>
+      </c>
+      <c r="AP63">
+        <v>15.449850579664741</v>
+      </c>
+      <c r="AQ63">
+        <v>15.449850579664741</v>
+      </c>
+      <c r="AR63">
+        <v>0.9560270017562168</v>
+      </c>
+      <c r="AS63">
+        <v>547.26825314352357</v>
+      </c>
+      <c r="AT63">
+        <v>-0.55762192069566785</v>
+      </c>
+      <c r="AU63">
+        <v>0.2</v>
+      </c>
+      <c r="AV63" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR63">
+        <v>15.449850579664741</v>
+      </c>
+      <c r="BS63">
+        <v>0.9560270017562168</v>
+      </c>
+      <c r="BT63">
+        <v>15.449850579664741</v>
+      </c>
+      <c r="BU63">
+        <v>15.449850579664741</v>
+      </c>
+      <c r="BV63">
+        <v>0.9560270017562168</v>
+      </c>
+      <c r="BW63">
+        <v>547.26825314352357</v>
+      </c>
+      <c r="BX63">
+        <v>-0.55762192069566785</v>
+      </c>
+    </row>
+    <row r="64" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>225</v>
+      </c>
+      <c r="B64" t="s">
+        <v>226</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64" t="s">
+        <v>97</v>
+      </c>
+      <c r="E64" t="s">
+        <v>79</v>
+      </c>
+      <c r="F64">
+        <v>16590</v>
+      </c>
+      <c r="G64">
+        <v>4.5</v>
+      </c>
+      <c r="H64" t="s">
+        <v>199</v>
+      </c>
+      <c r="I64" t="s">
+        <v>81</v>
+      </c>
+      <c r="J64">
+        <v>5</v>
+      </c>
+      <c r="K64">
+        <v>5</v>
+      </c>
+      <c r="L64" t="s">
+        <v>82</v>
+      </c>
+      <c r="M64" t="b">
+        <v>1</v>
+      </c>
+      <c r="N64" t="b">
+        <v>0</v>
+      </c>
+      <c r="O64" t="b">
+        <v>0</v>
+      </c>
+      <c r="P64" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>222</v>
+      </c>
+      <c r="R64">
+        <v>1</v>
+      </c>
+      <c r="S64" t="s">
+        <v>85</v>
+      </c>
+      <c r="T64" t="s">
+        <v>86</v>
+      </c>
+      <c r="U64" t="s">
+        <v>87</v>
+      </c>
+      <c r="V64">
+        <v>3</v>
+      </c>
+      <c r="W64" t="s">
+        <v>201</v>
+      </c>
+      <c r="X64" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z64">
+        <v>4000</v>
+      </c>
+      <c r="AA64">
+        <v>4000</v>
+      </c>
+      <c r="AC64">
+        <v>256</v>
+      </c>
+      <c r="AD64" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE64">
+        <v>0.15</v>
+      </c>
+      <c r="AF64" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG64">
+        <v>60</v>
+      </c>
+      <c r="AH64">
+        <v>30</v>
+      </c>
+      <c r="AI64">
+        <v>30</v>
+      </c>
+      <c r="AJ64">
+        <v>4.4807172623616998E-2</v>
+      </c>
+      <c r="AK64">
+        <v>13.49298940399798</v>
+      </c>
+      <c r="AL64">
+        <v>0.95954534942442482</v>
+      </c>
+      <c r="AM64">
+        <v>-0.38436834586904339</v>
+      </c>
+      <c r="AN64">
+        <v>17.850014098120869</v>
+      </c>
+      <c r="AO64">
+        <v>0.949195713282736</v>
+      </c>
+      <c r="AP64">
+        <v>17.850014098120869</v>
+      </c>
+      <c r="AQ64">
+        <v>17.850014098120869</v>
+      </c>
+      <c r="AR64">
+        <v>0.949195713282736</v>
+      </c>
+      <c r="AS64">
+        <v>472.59543286102883</v>
+      </c>
+      <c r="AT64">
+        <v>-0.3450899108740082</v>
+      </c>
+      <c r="AU64">
+        <v>0.2</v>
+      </c>
+      <c r="AV64" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR64">
+        <v>17.850014098120869</v>
+      </c>
+      <c r="BS64">
+        <v>0.949195713282736</v>
+      </c>
+      <c r="BT64">
+        <v>17.850014098120869</v>
+      </c>
+      <c r="BU64">
+        <v>17.850014098120869</v>
+      </c>
+      <c r="BV64">
+        <v>0.949195713282736</v>
+      </c>
+      <c r="BW64">
+        <v>472.59543286102883</v>
+      </c>
+      <c r="BX64">
+        <v>-0.3450899108740082</v>
+      </c>
+    </row>
+    <row r="65" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>227</v>
+      </c>
+      <c r="B65" t="s">
+        <v>228</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
+      </c>
+      <c r="D65" t="s">
+        <v>97</v>
+      </c>
+      <c r="E65" t="s">
+        <v>79</v>
+      </c>
+      <c r="F65">
+        <v>16590</v>
+      </c>
+      <c r="G65">
+        <v>4.5</v>
+      </c>
+      <c r="H65" t="s">
+        <v>199</v>
+      </c>
+      <c r="I65" t="s">
+        <v>81</v>
+      </c>
+      <c r="J65">
+        <v>5</v>
+      </c>
+      <c r="K65">
+        <v>5</v>
+      </c>
+      <c r="L65" t="s">
+        <v>82</v>
+      </c>
+      <c r="M65" t="b">
+        <v>1</v>
+      </c>
+      <c r="N65" t="b">
+        <v>0</v>
+      </c>
+      <c r="O65" t="b">
+        <v>0</v>
+      </c>
+      <c r="P65" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>222</v>
+      </c>
+      <c r="R65">
+        <v>1</v>
+      </c>
+      <c r="S65" t="s">
+        <v>85</v>
+      </c>
+      <c r="T65" t="s">
+        <v>86</v>
+      </c>
+      <c r="U65" t="s">
+        <v>87</v>
+      </c>
+      <c r="V65">
+        <v>3</v>
+      </c>
+      <c r="W65" t="s">
+        <v>201</v>
+      </c>
+      <c r="X65" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z65">
+        <v>4000</v>
+      </c>
+      <c r="AA65">
+        <v>4000</v>
+      </c>
+      <c r="AC65">
+        <v>256</v>
+      </c>
+      <c r="AD65" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE65">
+        <v>0.15</v>
+      </c>
+      <c r="AF65" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG65">
+        <v>60</v>
+      </c>
+      <c r="AH65">
+        <v>30</v>
+      </c>
+      <c r="AI65">
+        <v>30</v>
+      </c>
+      <c r="AJ65">
+        <v>4.19660558575232E-2</v>
+      </c>
+      <c r="AK65">
+        <v>7.7440577950578726</v>
+      </c>
+      <c r="AL65">
+        <v>0.97678178328345078</v>
+      </c>
+      <c r="AM65">
+        <v>-1.0310931277351949</v>
+      </c>
+      <c r="AN65">
+        <v>10.43612768758244</v>
+      </c>
+      <c r="AO65">
+        <v>0.97029694092433638</v>
+      </c>
+      <c r="AP65">
+        <v>10.43612768758244</v>
+      </c>
+      <c r="AQ65">
+        <v>10.43612768758244</v>
+      </c>
+      <c r="AR65">
+        <v>0.97029694092433638</v>
+      </c>
+      <c r="AS65">
+        <v>690.87274731105333</v>
+      </c>
+      <c r="AT65">
+        <v>-0.96634562564461202</v>
+      </c>
+      <c r="AU65">
+        <v>0.2</v>
+      </c>
+      <c r="AV65" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR65">
+        <v>10.43612768758244</v>
+      </c>
+      <c r="BS65">
+        <v>0.97029694092433638</v>
+      </c>
+      <c r="BT65">
+        <v>10.43612768758244</v>
+      </c>
+      <c r="BU65">
+        <v>10.43612768758244</v>
+      </c>
+      <c r="BV65">
+        <v>0.97029694092433638</v>
+      </c>
+      <c r="BW65">
+        <v>690.87274731105333</v>
+      </c>
+      <c r="BX65">
+        <v>-0.96634562564461202</v>
+      </c>
+    </row>
+    <row r="66" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>229</v>
+      </c>
+      <c r="B66" t="s">
+        <v>230</v>
+      </c>
+      <c r="C66">
+        <v>4</v>
+      </c>
+      <c r="D66" t="s">
+        <v>78</v>
+      </c>
+      <c r="E66" t="s">
+        <v>79</v>
+      </c>
+      <c r="F66">
+        <v>16590</v>
+      </c>
+      <c r="G66">
+        <v>4.5</v>
+      </c>
+      <c r="H66" t="s">
+        <v>199</v>
+      </c>
+      <c r="I66" t="s">
+        <v>81</v>
+      </c>
+      <c r="J66">
+        <v>5</v>
+      </c>
+      <c r="K66">
+        <v>5</v>
+      </c>
+      <c r="L66" t="s">
+        <v>82</v>
+      </c>
+      <c r="M66" t="b">
+        <v>1</v>
+      </c>
+      <c r="N66" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66" t="b">
+        <v>0</v>
+      </c>
+      <c r="P66" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>222</v>
+      </c>
+      <c r="R66">
+        <v>1</v>
+      </c>
+      <c r="S66" t="s">
+        <v>85</v>
+      </c>
+      <c r="T66" t="s">
+        <v>86</v>
+      </c>
+      <c r="U66" t="s">
+        <v>87</v>
+      </c>
+      <c r="V66">
+        <v>3</v>
+      </c>
+      <c r="W66" t="s">
+        <v>201</v>
+      </c>
+      <c r="X66" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z66">
+        <v>4000</v>
+      </c>
+      <c r="AA66">
+        <v>4000</v>
+      </c>
+      <c r="AC66">
+        <v>256</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE66">
+        <v>0.15</v>
+      </c>
+      <c r="AF66" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG66">
+        <v>60</v>
+      </c>
+      <c r="AH66">
+        <v>30</v>
+      </c>
+      <c r="AI66">
+        <v>30</v>
+      </c>
+      <c r="AJ66">
+        <v>4.9762633438750203E-2</v>
+      </c>
+      <c r="AK66">
+        <v>13.840749641855581</v>
+      </c>
+      <c r="AL66">
+        <v>0.95850269545906719</v>
+      </c>
+      <c r="AM66">
+        <v>-0.38309558443557701</v>
+      </c>
+      <c r="AN66">
+        <v>17.936860222398511</v>
+      </c>
+      <c r="AO66">
+        <v>0.9489485339038386</v>
+      </c>
+      <c r="AP66">
+        <v>17.936860222398511</v>
+      </c>
+      <c r="AQ66">
+        <v>17.936860222398511</v>
+      </c>
+      <c r="AR66">
+        <v>0.9489485339038386</v>
+      </c>
+      <c r="AS66">
+        <v>482.15050878280817</v>
+      </c>
+      <c r="AT66">
+        <v>-0.37228534131271052</v>
+      </c>
+      <c r="AU66">
+        <v>0.2</v>
+      </c>
+      <c r="AV66" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR66">
+        <v>17.936860222398511</v>
+      </c>
+      <c r="BS66">
+        <v>0.9489485339038386</v>
+      </c>
+      <c r="BT66">
+        <v>17.936860222398511</v>
+      </c>
+      <c r="BU66">
+        <v>17.936860222398511</v>
+      </c>
+      <c r="BV66">
+        <v>0.9489485339038386</v>
+      </c>
+      <c r="BW66">
+        <v>482.15050878280817</v>
+      </c>
+      <c r="BX66">
+        <v>-0.37228534131271052</v>
+      </c>
+    </row>
+    <row r="67" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>231</v>
+      </c>
+      <c r="B67" t="s">
+        <v>232</v>
+      </c>
+      <c r="C67">
+        <v>5</v>
+      </c>
+      <c r="D67" t="s">
+        <v>78</v>
+      </c>
+      <c r="E67" t="s">
+        <v>79</v>
+      </c>
+      <c r="F67">
+        <v>16590</v>
+      </c>
+      <c r="G67">
+        <v>4.5</v>
+      </c>
+      <c r="H67" t="s">
+        <v>199</v>
+      </c>
+      <c r="I67" t="s">
+        <v>81</v>
+      </c>
+      <c r="J67">
+        <v>5</v>
+      </c>
+      <c r="K67">
+        <v>5</v>
+      </c>
+      <c r="L67" t="s">
+        <v>82</v>
+      </c>
+      <c r="M67" t="b">
+        <v>1</v>
+      </c>
+      <c r="N67" t="b">
+        <v>0</v>
+      </c>
+      <c r="O67" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>222</v>
+      </c>
+      <c r="R67">
+        <v>1</v>
+      </c>
+      <c r="S67" t="s">
+        <v>85</v>
+      </c>
+      <c r="T67" t="s">
+        <v>86</v>
+      </c>
+      <c r="U67" t="s">
+        <v>87</v>
+      </c>
+      <c r="V67">
+        <v>3</v>
+      </c>
+      <c r="W67" t="s">
+        <v>201</v>
+      </c>
+      <c r="X67" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z67">
+        <v>4000</v>
+      </c>
+      <c r="AA67">
+        <v>4000</v>
+      </c>
+      <c r="AC67">
+        <v>256</v>
+      </c>
+      <c r="AD67" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE67">
+        <v>0.15</v>
+      </c>
+      <c r="AF67" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG67">
+        <v>60</v>
+      </c>
+      <c r="AH67">
+        <v>30</v>
+      </c>
+      <c r="AI67">
+        <v>30</v>
+      </c>
+      <c r="AJ67">
+        <v>5.2988112802633998E-2</v>
+      </c>
+      <c r="AK67">
+        <v>12.02885377924304</v>
+      </c>
+      <c r="AL67">
+        <v>0.96393511757151618</v>
+      </c>
+      <c r="AM67">
+        <v>-0.45034989442469398</v>
+      </c>
+      <c r="AN67">
+        <v>15.056692911027881</v>
+      </c>
+      <c r="AO67">
+        <v>0.95714599778684839</v>
+      </c>
+      <c r="AP67">
+        <v>15.056692911027881</v>
+      </c>
+      <c r="AQ67">
+        <v>15.056692911027881</v>
+      </c>
+      <c r="AR67">
+        <v>0.95714599778684839</v>
+      </c>
+      <c r="AS67">
+        <v>505.06795376309748</v>
+      </c>
+      <c r="AT67">
+        <v>-0.43751242960550418</v>
+      </c>
+      <c r="AU67">
+        <v>0.2</v>
+      </c>
+      <c r="AV67" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR67">
+        <v>15.056692911027881</v>
+      </c>
+      <c r="BS67">
+        <v>0.95714599778684839</v>
+      </c>
+      <c r="BT67">
+        <v>15.056692911027881</v>
+      </c>
+      <c r="BU67">
+        <v>15.056692911027881</v>
+      </c>
+      <c r="BV67">
+        <v>0.95714599778684839</v>
+      </c>
+      <c r="BW67">
+        <v>505.06795376309748</v>
+      </c>
+      <c r="BX67">
+        <v>-0.43751242960550418</v>
+      </c>
+    </row>
+    <row r="68" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>233</v>
+      </c>
+      <c r="B68" t="s">
+        <v>234</v>
+      </c>
+      <c r="C68">
+        <v>6</v>
+      </c>
+      <c r="D68" t="s">
+        <v>78</v>
+      </c>
+      <c r="E68" t="s">
+        <v>79</v>
+      </c>
+      <c r="F68">
+        <v>16590</v>
+      </c>
+      <c r="G68">
+        <v>4.5</v>
+      </c>
+      <c r="H68" t="s">
+        <v>199</v>
+      </c>
+      <c r="I68" t="s">
+        <v>81</v>
+      </c>
+      <c r="J68">
+        <v>5</v>
+      </c>
+      <c r="K68">
+        <v>5</v>
+      </c>
+      <c r="L68" t="s">
+        <v>82</v>
+      </c>
+      <c r="M68" t="b">
+        <v>1</v>
+      </c>
+      <c r="N68" t="b">
+        <v>0</v>
+      </c>
+      <c r="O68" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>222</v>
+      </c>
+      <c r="R68">
+        <v>1</v>
+      </c>
+      <c r="S68" t="s">
+        <v>85</v>
+      </c>
+      <c r="T68" t="s">
+        <v>86</v>
+      </c>
+      <c r="U68" t="s">
+        <v>87</v>
+      </c>
+      <c r="V68">
+        <v>3</v>
+      </c>
+      <c r="W68" t="s">
+        <v>201</v>
+      </c>
+      <c r="X68" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z68">
+        <v>4000</v>
+      </c>
+      <c r="AA68">
+        <v>4000</v>
+      </c>
+      <c r="AC68">
+        <v>256</v>
+      </c>
+      <c r="AD68" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE68">
+        <v>0.15</v>
+      </c>
+      <c r="AF68" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG68">
+        <v>60</v>
+      </c>
+      <c r="AH68">
+        <v>30</v>
+      </c>
+      <c r="AI68">
+        <v>30</v>
+      </c>
+      <c r="AJ68">
+        <v>4.3672558209668803E-2</v>
+      </c>
+      <c r="AK68">
+        <v>10.307239191809661</v>
+      </c>
+      <c r="AL68">
+        <v>0.96909685856716199</v>
+      </c>
+      <c r="AM68">
+        <v>-0.73148871718562547</v>
+      </c>
+      <c r="AN68">
+        <v>14.144059823761109</v>
+      </c>
+      <c r="AO68">
+        <v>0.95974351243183942</v>
+      </c>
+      <c r="AP68">
+        <v>14.144059823761109</v>
+      </c>
+      <c r="AQ68">
+        <v>14.144059823761109</v>
+      </c>
+      <c r="AR68">
+        <v>0.95974351243183942</v>
+      </c>
+      <c r="AS68">
+        <v>609.18186437815234</v>
+      </c>
+      <c r="AT68">
+        <v>-0.73383897237835716</v>
+      </c>
+      <c r="AU68">
+        <v>0.2</v>
+      </c>
+      <c r="AV68" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR68">
+        <v>14.144059823761109</v>
+      </c>
+      <c r="BS68">
+        <v>0.95974351243183942</v>
+      </c>
+      <c r="BT68">
+        <v>14.144059823761109</v>
+      </c>
+      <c r="BU68">
+        <v>14.144059823761109</v>
+      </c>
+      <c r="BV68">
+        <v>0.95974351243183942</v>
+      </c>
+      <c r="BW68">
+        <v>609.18186437815234</v>
+      </c>
+      <c r="BX68">
+        <v>-0.73383897237835716</v>
+      </c>
+    </row>
+    <row r="69" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>235</v>
+      </c>
+      <c r="B69" t="s">
+        <v>236</v>
+      </c>
+      <c r="C69">
+        <v>7</v>
+      </c>
+      <c r="D69" t="s">
+        <v>78</v>
+      </c>
+      <c r="E69" t="s">
+        <v>79</v>
+      </c>
+      <c r="F69">
+        <v>16590</v>
+      </c>
+      <c r="G69">
+        <v>4.5</v>
+      </c>
+      <c r="H69" t="s">
+        <v>199</v>
+      </c>
+      <c r="I69" t="s">
+        <v>81</v>
+      </c>
+      <c r="J69">
+        <v>5</v>
+      </c>
+      <c r="K69">
+        <v>5</v>
+      </c>
+      <c r="L69" t="s">
+        <v>82</v>
+      </c>
+      <c r="M69" t="b">
+        <v>1</v>
+      </c>
+      <c r="N69" t="b">
+        <v>0</v>
+      </c>
+      <c r="O69" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>222</v>
+      </c>
+      <c r="R69">
+        <v>1</v>
+      </c>
+      <c r="S69" t="s">
+        <v>85</v>
+      </c>
+      <c r="T69" t="s">
+        <v>86</v>
+      </c>
+      <c r="U69" t="s">
+        <v>87</v>
+      </c>
+      <c r="V69">
+        <v>3</v>
+      </c>
+      <c r="W69" t="s">
+        <v>201</v>
+      </c>
+      <c r="X69" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z69">
+        <v>4000</v>
+      </c>
+      <c r="AA69">
+        <v>4000</v>
+      </c>
+      <c r="AC69">
+        <v>256</v>
+      </c>
+      <c r="AD69" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE69">
+        <v>0.15</v>
+      </c>
+      <c r="AF69" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG69">
+        <v>60</v>
+      </c>
+      <c r="AH69">
+        <v>30</v>
+      </c>
+      <c r="AI69">
+        <v>30</v>
+      </c>
+      <c r="AJ69">
+        <v>5.2030213751537401E-2</v>
+      </c>
+      <c r="AK69">
+        <v>8.8771562855018082</v>
+      </c>
+      <c r="AL69">
+        <v>0.97338452993016222</v>
+      </c>
+      <c r="AM69">
+        <v>-0.22933283932982501</v>
+      </c>
+      <c r="AN69">
+        <v>12.28857080051313</v>
+      </c>
+      <c r="AO69">
+        <v>0.96502456127693537</v>
+      </c>
+      <c r="AP69">
+        <v>12.28857080051313</v>
+      </c>
+      <c r="AQ69">
+        <v>12.28857080051313</v>
+      </c>
+      <c r="AR69">
+        <v>0.96502456127693537</v>
+      </c>
+      <c r="AS69">
+        <v>445.82502196278142</v>
+      </c>
+      <c r="AT69">
+        <v>-0.26889660237927071</v>
+      </c>
+      <c r="AU69">
+        <v>0.2</v>
+      </c>
+      <c r="AV69" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR69">
+        <v>12.28857080051313</v>
+      </c>
+      <c r="BS69">
+        <v>0.96502456127693537</v>
+      </c>
+      <c r="BT69">
+        <v>12.28857080051313</v>
+      </c>
+      <c r="BU69">
+        <v>12.28857080051313</v>
+      </c>
+      <c r="BV69">
+        <v>0.96502456127693537</v>
+      </c>
+      <c r="BW69">
+        <v>445.82502196278142</v>
+      </c>
+      <c r="BX69">
+        <v>-0.26889660237927071</v>
+      </c>
+    </row>
+    <row r="70" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>237</v>
+      </c>
+      <c r="B70" t="s">
+        <v>238</v>
+      </c>
+      <c r="C70">
+        <v>8</v>
+      </c>
+      <c r="D70" t="s">
+        <v>97</v>
+      </c>
+      <c r="E70" t="s">
+        <v>79</v>
+      </c>
+      <c r="F70">
+        <v>16590</v>
+      </c>
+      <c r="G70">
+        <v>4.5</v>
+      </c>
+      <c r="H70" t="s">
+        <v>199</v>
+      </c>
+      <c r="I70" t="s">
+        <v>81</v>
+      </c>
+      <c r="J70">
+        <v>5</v>
+      </c>
+      <c r="K70">
+        <v>5</v>
+      </c>
+      <c r="L70" t="s">
+        <v>82</v>
+      </c>
+      <c r="M70" t="b">
+        <v>1</v>
+      </c>
+      <c r="N70" t="b">
+        <v>0</v>
+      </c>
+      <c r="O70" t="b">
+        <v>0</v>
+      </c>
+      <c r="P70" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>222</v>
+      </c>
+      <c r="R70">
+        <v>1</v>
+      </c>
+      <c r="S70" t="s">
+        <v>85</v>
+      </c>
+      <c r="T70" t="s">
+        <v>86</v>
+      </c>
+      <c r="U70" t="s">
+        <v>87</v>
+      </c>
+      <c r="V70">
+        <v>3</v>
+      </c>
+      <c r="W70" t="s">
+        <v>201</v>
+      </c>
+      <c r="X70" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z70">
+        <v>4000</v>
+      </c>
+      <c r="AA70">
+        <v>4000</v>
+      </c>
+      <c r="AC70">
+        <v>256</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE70">
+        <v>0.15</v>
+      </c>
+      <c r="AF70" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG70">
+        <v>60</v>
+      </c>
+      <c r="AH70">
+        <v>30</v>
+      </c>
+      <c r="AI70">
+        <v>30</v>
+      </c>
+      <c r="AJ70">
+        <v>6.3973457900765196E-2</v>
+      </c>
+      <c r="AK70">
+        <v>9.8246069341337474</v>
+      </c>
+      <c r="AL70">
+        <v>0.97054388551991377</v>
+      </c>
+      <c r="AM70">
+        <v>-5.0574616377070801E-2</v>
+      </c>
+      <c r="AN70">
+        <v>13.897281032161761</v>
+      </c>
+      <c r="AO70">
+        <v>0.96044588837480704</v>
+      </c>
+      <c r="AP70">
+        <v>13.897281032161761</v>
+      </c>
+      <c r="AQ70">
+        <v>13.897281032161761</v>
+      </c>
+      <c r="AR70">
+        <v>0.96044588837480704</v>
+      </c>
+      <c r="AS70">
+        <v>373.69727105100691</v>
+      </c>
+      <c r="AT70">
+        <v>-6.3608308630586696E-2</v>
+      </c>
+      <c r="AU70">
+        <v>0.2</v>
+      </c>
+      <c r="AV70" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR70">
+        <v>13.897281032161761</v>
+      </c>
+      <c r="BS70">
+        <v>0.96044588837480704</v>
+      </c>
+      <c r="BT70">
+        <v>13.897281032161761</v>
+      </c>
+      <c r="BU70">
+        <v>13.897281032161761</v>
+      </c>
+      <c r="BV70">
+        <v>0.96044588837480704</v>
+      </c>
+      <c r="BW70">
+        <v>373.69727105100691</v>
+      </c>
+      <c r="BX70">
+        <v>-6.3608308630586696E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>239</v>
+      </c>
+      <c r="B71" t="s">
+        <v>240</v>
+      </c>
+      <c r="C71">
+        <v>9</v>
+      </c>
+      <c r="D71" t="s">
+        <v>78</v>
+      </c>
+      <c r="E71" t="s">
+        <v>79</v>
+      </c>
+      <c r="F71">
+        <v>16590</v>
+      </c>
+      <c r="G71">
+        <v>4.5</v>
+      </c>
+      <c r="H71" t="s">
+        <v>199</v>
+      </c>
+      <c r="I71" t="s">
+        <v>81</v>
+      </c>
+      <c r="J71">
+        <v>5</v>
+      </c>
+      <c r="K71">
+        <v>5</v>
+      </c>
+      <c r="L71" t="s">
+        <v>82</v>
+      </c>
+      <c r="M71" t="b">
+        <v>1</v>
+      </c>
+      <c r="N71" t="b">
+        <v>0</v>
+      </c>
+      <c r="O71" t="b">
+        <v>0</v>
+      </c>
+      <c r="P71" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>222</v>
+      </c>
+      <c r="R71">
+        <v>1</v>
+      </c>
+      <c r="S71" t="s">
+        <v>85</v>
+      </c>
+      <c r="T71" t="s">
+        <v>86</v>
+      </c>
+      <c r="U71" t="s">
+        <v>87</v>
+      </c>
+      <c r="V71">
+        <v>3</v>
+      </c>
+      <c r="W71" t="s">
+        <v>201</v>
+      </c>
+      <c r="X71" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z71">
+        <v>4000</v>
+      </c>
+      <c r="AA71">
+        <v>4000</v>
+      </c>
+      <c r="AC71">
+        <v>256</v>
+      </c>
+      <c r="AD71" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE71">
+        <v>0.15</v>
+      </c>
+      <c r="AF71" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG71">
+        <v>60</v>
+      </c>
+      <c r="AH71">
+        <v>30</v>
+      </c>
+      <c r="AI71">
+        <v>30</v>
+      </c>
+      <c r="AJ71">
+        <v>5.3287233628539502E-2</v>
+      </c>
+      <c r="AK71">
+        <v>11.450744221834279</v>
+      </c>
+      <c r="AL71">
+        <v>0.96566840435023715</v>
+      </c>
+      <c r="AM71">
+        <v>-1.16763416628604E-2</v>
+      </c>
+      <c r="AN71">
+        <v>18.487639071267509</v>
+      </c>
+      <c r="AO71">
+        <v>0.94738092020886155</v>
+      </c>
+      <c r="AP71">
+        <v>18.487639071267509</v>
+      </c>
+      <c r="AQ71">
+        <v>18.487639071267509</v>
+      </c>
+      <c r="AR71">
+        <v>0.94738092020886155</v>
+      </c>
+      <c r="AS71">
+        <v>355.68093468929771</v>
+      </c>
+      <c r="AT71">
+        <v>-1.2330639431922001E-2</v>
+      </c>
+      <c r="AU71">
+        <v>0.2</v>
+      </c>
+      <c r="AV71" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR71">
+        <v>18.487639071267509</v>
+      </c>
+      <c r="BS71">
+        <v>0.94738092020886155</v>
+      </c>
+      <c r="BT71">
+        <v>18.487639071267509</v>
+      </c>
+      <c r="BU71">
+        <v>18.487639071267509</v>
+      </c>
+      <c r="BV71">
+        <v>0.94738092020886155</v>
+      </c>
+      <c r="BW71">
+        <v>355.68093468929771</v>
+      </c>
+      <c r="BX71">
+        <v>-1.2330639431922001E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>241</v>
+      </c>
+      <c r="B72" t="s">
+        <v>242</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72" t="s">
+        <v>78</v>
+      </c>
+      <c r="E72" t="s">
+        <v>79</v>
+      </c>
+      <c r="F72">
+        <v>16590</v>
+      </c>
+      <c r="G72">
+        <v>4.5</v>
+      </c>
+      <c r="H72" t="s">
+        <v>199</v>
+      </c>
+      <c r="I72" t="s">
+        <v>81</v>
+      </c>
+      <c r="J72">
+        <v>5</v>
+      </c>
+      <c r="K72">
+        <v>5</v>
+      </c>
+      <c r="L72" t="s">
+        <v>82</v>
+      </c>
+      <c r="M72" t="b">
+        <v>1</v>
+      </c>
+      <c r="N72" t="b">
+        <v>0</v>
+      </c>
+      <c r="O72" t="b">
+        <v>0</v>
+      </c>
+      <c r="P72" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>243</v>
+      </c>
+      <c r="R72">
+        <v>1</v>
+      </c>
+      <c r="S72" t="s">
+        <v>85</v>
+      </c>
+      <c r="T72" t="s">
+        <v>86</v>
+      </c>
+      <c r="U72" t="s">
+        <v>87</v>
+      </c>
+      <c r="V72">
+        <v>5</v>
+      </c>
+      <c r="W72" t="s">
+        <v>201</v>
+      </c>
+      <c r="X72" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z72">
+        <v>4000</v>
+      </c>
+      <c r="AA72">
+        <v>4000</v>
+      </c>
+      <c r="AC72">
+        <v>256</v>
+      </c>
+      <c r="AD72" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE72">
+        <v>0.15</v>
+      </c>
+      <c r="AF72" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG72">
+        <v>80</v>
+      </c>
+      <c r="AH72">
+        <v>50</v>
+      </c>
+      <c r="AI72">
+        <v>30</v>
+      </c>
+      <c r="AJ72">
+        <v>4.75144492153525E-2</v>
+      </c>
+      <c r="AK72">
+        <v>14.060896425098811</v>
+      </c>
+      <c r="AL72">
+        <v>0.95784265186718498</v>
+      </c>
+      <c r="AM72">
+        <v>-0.35488162732929068</v>
+      </c>
+      <c r="AN72">
+        <v>16.183668659121409</v>
+      </c>
+      <c r="AO72">
+        <v>0.95393842614489821</v>
+      </c>
+      <c r="AP72">
+        <v>16.183668659121409</v>
+      </c>
+      <c r="AQ72">
+        <v>16.183668659121409</v>
+      </c>
+      <c r="AR72">
+        <v>0.95393842614489821</v>
+      </c>
+      <c r="AS72">
+        <v>460.12175391430992</v>
+      </c>
+      <c r="AT72">
+        <v>-0.30958762173604493</v>
+      </c>
+      <c r="AU72">
+        <v>0.2</v>
+      </c>
+      <c r="AV72" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR72">
+        <v>16.183668659121409</v>
+      </c>
+      <c r="BS72">
+        <v>0.95393842614489821</v>
+      </c>
+      <c r="BT72">
+        <v>16.183668659121409</v>
+      </c>
+      <c r="BU72">
+        <v>16.183668659121409</v>
+      </c>
+      <c r="BV72">
+        <v>0.95393842614489821</v>
+      </c>
+      <c r="BW72">
+        <v>460.12175391430992</v>
+      </c>
+      <c r="BX72">
+        <v>-0.30958762173604493</v>
+      </c>
+    </row>
+    <row r="73" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>244</v>
+      </c>
+      <c r="B73" t="s">
+        <v>245</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73" t="s">
+        <v>97</v>
+      </c>
+      <c r="E73" t="s">
+        <v>79</v>
+      </c>
+      <c r="F73">
+        <v>16590</v>
+      </c>
+      <c r="G73">
+        <v>4.5</v>
+      </c>
+      <c r="H73" t="s">
+        <v>199</v>
+      </c>
+      <c r="I73" t="s">
+        <v>81</v>
+      </c>
+      <c r="J73">
+        <v>5</v>
+      </c>
+      <c r="K73">
+        <v>5</v>
+      </c>
+      <c r="L73" t="s">
+        <v>82</v>
+      </c>
+      <c r="M73" t="b">
+        <v>1</v>
+      </c>
+      <c r="N73" t="b">
+        <v>0</v>
+      </c>
+      <c r="O73" t="b">
+        <v>0</v>
+      </c>
+      <c r="P73" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>243</v>
+      </c>
+      <c r="R73">
+        <v>1</v>
+      </c>
+      <c r="S73" t="s">
+        <v>85</v>
+      </c>
+      <c r="T73" t="s">
+        <v>86</v>
+      </c>
+      <c r="U73" t="s">
+        <v>87</v>
+      </c>
+      <c r="V73">
+        <v>5</v>
+      </c>
+      <c r="W73" t="s">
+        <v>201</v>
+      </c>
+      <c r="X73" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z73">
+        <v>4000</v>
+      </c>
+      <c r="AA73">
+        <v>4000</v>
+      </c>
+      <c r="AC73">
+        <v>256</v>
+      </c>
+      <c r="AD73" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE73">
+        <v>0.15</v>
+      </c>
+      <c r="AF73" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG73">
+        <v>80</v>
+      </c>
+      <c r="AH73">
+        <v>50</v>
+      </c>
+      <c r="AI73">
+        <v>30</v>
+      </c>
+      <c r="AJ73">
+        <v>4.7524084001423397E-2</v>
+      </c>
+      <c r="AK73">
+        <v>15.450875031102809</v>
+      </c>
+      <c r="AL73">
+        <v>0.95367522112742942</v>
+      </c>
+      <c r="AM73">
+        <v>-7.5528444953792295E-2</v>
+      </c>
+      <c r="AN73">
+        <v>16.225166713169219</v>
+      </c>
+      <c r="AO73">
+        <v>0.9538203153678162</v>
+      </c>
+      <c r="AP73">
+        <v>16.225166713169219</v>
+      </c>
+      <c r="AQ73">
+        <v>16.225166713169219</v>
+      </c>
+      <c r="AR73">
+        <v>0.9538203153678162</v>
+      </c>
+      <c r="AS73">
+        <v>374.74153992916081</v>
+      </c>
+      <c r="AT73">
+        <v>-6.6580481941151903E-2</v>
+      </c>
+      <c r="AU73">
+        <v>0.2</v>
+      </c>
+      <c r="AV73" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR73">
+        <v>16.225166713169219</v>
+      </c>
+      <c r="BS73">
+        <v>0.9538203153678162</v>
+      </c>
+      <c r="BT73">
+        <v>16.225166713169219</v>
+      </c>
+      <c r="BU73">
+        <v>16.225166713169219</v>
+      </c>
+      <c r="BV73">
+        <v>0.9538203153678162</v>
+      </c>
+      <c r="BW73">
+        <v>374.74153992916081</v>
+      </c>
+      <c r="BX73">
+        <v>-6.6580481941151903E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>246</v>
+      </c>
+      <c r="B74" t="s">
+        <v>247</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+      <c r="D74" t="s">
+        <v>78</v>
+      </c>
+      <c r="E74" t="s">
+        <v>79</v>
+      </c>
+      <c r="F74">
+        <v>16590</v>
+      </c>
+      <c r="G74">
+        <v>4.5</v>
+      </c>
+      <c r="H74" t="s">
+        <v>199</v>
+      </c>
+      <c r="I74" t="s">
+        <v>81</v>
+      </c>
+      <c r="J74">
+        <v>5</v>
+      </c>
+      <c r="K74">
+        <v>5</v>
+      </c>
+      <c r="L74" t="s">
+        <v>82</v>
+      </c>
+      <c r="M74" t="b">
+        <v>1</v>
+      </c>
+      <c r="N74" t="b">
+        <v>0</v>
+      </c>
+      <c r="O74" t="b">
+        <v>0</v>
+      </c>
+      <c r="P74" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>243</v>
+      </c>
+      <c r="R74">
+        <v>1</v>
+      </c>
+      <c r="S74" t="s">
+        <v>85</v>
+      </c>
+      <c r="T74" t="s">
+        <v>86</v>
+      </c>
+      <c r="U74" t="s">
+        <v>87</v>
+      </c>
+      <c r="V74">
+        <v>5</v>
+      </c>
+      <c r="W74" t="s">
+        <v>201</v>
+      </c>
+      <c r="X74" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z74">
+        <v>4000</v>
+      </c>
+      <c r="AA74">
+        <v>4000</v>
+      </c>
+      <c r="AC74">
+        <v>256</v>
+      </c>
+      <c r="AD74" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE74">
+        <v>0.15</v>
+      </c>
+      <c r="AF74" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG74">
+        <v>80</v>
+      </c>
+      <c r="AH74">
+        <v>50</v>
+      </c>
+      <c r="AI74">
+        <v>30</v>
+      </c>
+      <c r="AJ74">
+        <v>5.6414274049048897E-2</v>
+      </c>
+      <c r="AK74">
+        <v>19.529998713858539</v>
+      </c>
+      <c r="AL74">
+        <v>0.94144520164845902</v>
+      </c>
+      <c r="AM74">
+        <v>-0.78859905629171378</v>
+      </c>
+      <c r="AN74">
+        <v>22.398163909587929</v>
+      </c>
+      <c r="AO74">
+        <v>0.9362508771731014</v>
+      </c>
+      <c r="AP74">
+        <v>22.398163909587929</v>
+      </c>
+      <c r="AQ74">
+        <v>22.398163909587929</v>
+      </c>
+      <c r="AR74">
+        <v>0.9362508771731014</v>
+      </c>
+      <c r="AS74">
+        <v>1527.6475458353959</v>
+      </c>
+      <c r="AT74">
+        <v>-3.3479542086029221</v>
+      </c>
+      <c r="AU74">
+        <v>0.2</v>
+      </c>
+      <c r="AV74" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR74">
+        <v>22.398163909587929</v>
+      </c>
+      <c r="BS74">
+        <v>0.9362508771731014</v>
+      </c>
+      <c r="BT74">
+        <v>22.398163909587929</v>
+      </c>
+      <c r="BU74">
+        <v>22.398163909587929</v>
+      </c>
+      <c r="BV74">
+        <v>0.9362508771731014</v>
+      </c>
+      <c r="BW74">
+        <v>1527.6475458353959</v>
+      </c>
+      <c r="BX74">
+        <v>-3.3479542086029221</v>
+      </c>
+    </row>
+    <row r="75" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>248</v>
+      </c>
+      <c r="B75" t="s">
+        <v>249</v>
+      </c>
+      <c r="C75">
+        <v>3</v>
+      </c>
+      <c r="D75" t="s">
+        <v>78</v>
+      </c>
+      <c r="E75" t="s">
+        <v>79</v>
+      </c>
+      <c r="F75">
+        <v>16590</v>
+      </c>
+      <c r="G75">
+        <v>4.5</v>
+      </c>
+      <c r="H75" t="s">
+        <v>199</v>
+      </c>
+      <c r="I75" t="s">
+        <v>81</v>
+      </c>
+      <c r="J75">
+        <v>5</v>
+      </c>
+      <c r="K75">
+        <v>5</v>
+      </c>
+      <c r="L75" t="s">
+        <v>82</v>
+      </c>
+      <c r="M75" t="b">
+        <v>1</v>
+      </c>
+      <c r="N75" t="b">
+        <v>0</v>
+      </c>
+      <c r="O75" t="b">
+        <v>0</v>
+      </c>
+      <c r="P75" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>243</v>
+      </c>
+      <c r="R75">
+        <v>1</v>
+      </c>
+      <c r="S75" t="s">
+        <v>85</v>
+      </c>
+      <c r="T75" t="s">
+        <v>86</v>
+      </c>
+      <c r="U75" t="s">
+        <v>87</v>
+      </c>
+      <c r="V75">
+        <v>5</v>
+      </c>
+      <c r="W75" t="s">
+        <v>201</v>
+      </c>
+      <c r="X75" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z75">
+        <v>4000</v>
+      </c>
+      <c r="AA75">
+        <v>4000</v>
+      </c>
+      <c r="AC75">
+        <v>256</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE75">
+        <v>0.15</v>
+      </c>
+      <c r="AF75" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG75">
+        <v>80</v>
+      </c>
+      <c r="AH75">
+        <v>50</v>
+      </c>
+      <c r="AI75">
+        <v>30</v>
+      </c>
+      <c r="AJ75">
+        <v>4.3491384508493901E-2</v>
+      </c>
+      <c r="AK75">
+        <v>14.48083916563613</v>
+      </c>
+      <c r="AL75">
+        <v>0.9565835804841486</v>
+      </c>
+      <c r="AM75">
+        <v>-0.9376424149341448</v>
+      </c>
+      <c r="AN75">
+        <v>16.775494814616561</v>
+      </c>
+      <c r="AO75">
+        <v>0.95225398457945876</v>
+      </c>
+      <c r="AP75">
+        <v>16.775494814616561</v>
+      </c>
+      <c r="AQ75">
+        <v>16.775494814616561</v>
+      </c>
+      <c r="AR75">
+        <v>0.95225398457945876</v>
+      </c>
+      <c r="AS75">
+        <v>679.61481649941993</v>
+      </c>
+      <c r="AT75">
+        <v>-0.93430357001074238</v>
+      </c>
+      <c r="AU75">
+        <v>0.2</v>
+      </c>
+      <c r="AV75" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR75">
+        <v>16.775494814616561</v>
+      </c>
+      <c r="BS75">
+        <v>0.95225398457945876</v>
+      </c>
+      <c r="BT75">
+        <v>16.775494814616561</v>
+      </c>
+      <c r="BU75">
+        <v>16.775494814616561</v>
+      </c>
+      <c r="BV75">
+        <v>0.95225398457945876</v>
+      </c>
+      <c r="BW75">
+        <v>679.61481649941993</v>
+      </c>
+      <c r="BX75">
+        <v>-0.93430357001074238</v>
+      </c>
+    </row>
+    <row r="76" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>250</v>
+      </c>
+      <c r="B76" t="s">
+        <v>251</v>
+      </c>
+      <c r="C76">
+        <v>4</v>
+      </c>
+      <c r="D76" t="s">
+        <v>97</v>
+      </c>
+      <c r="E76" t="s">
+        <v>79</v>
+      </c>
+      <c r="F76">
+        <v>16590</v>
+      </c>
+      <c r="G76">
+        <v>4.5</v>
+      </c>
+      <c r="H76" t="s">
+        <v>199</v>
+      </c>
+      <c r="I76" t="s">
+        <v>81</v>
+      </c>
+      <c r="J76">
+        <v>5</v>
+      </c>
+      <c r="K76">
+        <v>5</v>
+      </c>
+      <c r="L76" t="s">
+        <v>82</v>
+      </c>
+      <c r="M76" t="b">
+        <v>1</v>
+      </c>
+      <c r="N76" t="b">
+        <v>0</v>
+      </c>
+      <c r="O76" t="b">
+        <v>0</v>
+      </c>
+      <c r="P76" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>243</v>
+      </c>
+      <c r="R76">
+        <v>1</v>
+      </c>
+      <c r="S76" t="s">
+        <v>85</v>
+      </c>
+      <c r="T76" t="s">
+        <v>86</v>
+      </c>
+      <c r="U76" t="s">
+        <v>87</v>
+      </c>
+      <c r="V76">
+        <v>5</v>
+      </c>
+      <c r="W76" t="s">
+        <v>201</v>
+      </c>
+      <c r="X76" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z76">
+        <v>4000</v>
+      </c>
+      <c r="AA76">
+        <v>4000</v>
+      </c>
+      <c r="AC76">
+        <v>256</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE76">
+        <v>0.15</v>
+      </c>
+      <c r="AF76" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG76">
+        <v>80</v>
+      </c>
+      <c r="AH76">
+        <v>50</v>
+      </c>
+      <c r="AI76">
+        <v>30</v>
+      </c>
+      <c r="AJ76">
+        <v>5.2385016179553302E-2</v>
+      </c>
+      <c r="AK76">
+        <v>16.2596596270809</v>
+      </c>
+      <c r="AL76">
+        <v>0.95125032496531525</v>
+      </c>
+      <c r="AM76">
+        <v>-0.17970506589140359</v>
+      </c>
+      <c r="AN76">
+        <v>20.150111876424312</v>
+      </c>
+      <c r="AO76">
+        <v>0.94264922954528219</v>
+      </c>
+      <c r="AP76">
+        <v>20.150111876424312</v>
+      </c>
+      <c r="AQ76">
+        <v>20.150111876424312</v>
+      </c>
+      <c r="AR76">
+        <v>0.94264922954528219</v>
+      </c>
+      <c r="AS76">
+        <v>416.04593872148291</v>
+      </c>
+      <c r="AT76">
+        <v>-0.18414008202854079</v>
+      </c>
+      <c r="AU76">
+        <v>0.2</v>
+      </c>
+      <c r="AV76" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR76">
+        <v>20.150111876424312</v>
+      </c>
+      <c r="BS76">
+        <v>0.94264922954528219</v>
+      </c>
+      <c r="BT76">
+        <v>20.150111876424312</v>
+      </c>
+      <c r="BU76">
+        <v>20.150111876424312</v>
+      </c>
+      <c r="BV76">
+        <v>0.94264922954528219</v>
+      </c>
+      <c r="BW76">
+        <v>416.04593872148291</v>
+      </c>
+      <c r="BX76">
+        <v>-0.18414008202854079</v>
+      </c>
+    </row>
+    <row r="77" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>252</v>
+      </c>
+      <c r="B77" t="s">
+        <v>253</v>
+      </c>
+      <c r="C77">
+        <v>5</v>
+      </c>
+      <c r="D77" t="s">
+        <v>97</v>
+      </c>
+      <c r="E77" t="s">
+        <v>79</v>
+      </c>
+      <c r="F77">
+        <v>16590</v>
+      </c>
+      <c r="G77">
+        <v>4.5</v>
+      </c>
+      <c r="H77" t="s">
+        <v>199</v>
+      </c>
+      <c r="I77" t="s">
+        <v>81</v>
+      </c>
+      <c r="J77">
+        <v>5</v>
+      </c>
+      <c r="K77">
+        <v>5</v>
+      </c>
+      <c r="L77" t="s">
+        <v>82</v>
+      </c>
+      <c r="M77" t="b">
+        <v>1</v>
+      </c>
+      <c r="N77" t="b">
+        <v>0</v>
+      </c>
+      <c r="O77" t="b">
+        <v>0</v>
+      </c>
+      <c r="P77" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>243</v>
+      </c>
+      <c r="R77">
+        <v>1</v>
+      </c>
+      <c r="S77" t="s">
+        <v>85</v>
+      </c>
+      <c r="T77" t="s">
+        <v>86</v>
+      </c>
+      <c r="U77" t="s">
+        <v>87</v>
+      </c>
+      <c r="V77">
+        <v>5</v>
+      </c>
+      <c r="W77" t="s">
+        <v>201</v>
+      </c>
+      <c r="X77" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z77">
+        <v>4000</v>
+      </c>
+      <c r="AA77">
+        <v>4000</v>
+      </c>
+      <c r="AC77">
+        <v>256</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE77">
+        <v>0.15</v>
+      </c>
+      <c r="AF77" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG77">
+        <v>80</v>
+      </c>
+      <c r="AH77">
+        <v>50</v>
+      </c>
+      <c r="AI77">
+        <v>30</v>
+      </c>
+      <c r="AJ77">
+        <v>4.54845991199503E-2</v>
+      </c>
+      <c r="AK77">
+        <v>18.325743024120921</v>
+      </c>
+      <c r="AL77">
+        <v>0.9450557983571134</v>
+      </c>
+      <c r="AM77">
+        <v>-0.14442421302849001</v>
+      </c>
+      <c r="AN77">
+        <v>18.612661914385601</v>
+      </c>
+      <c r="AO77">
+        <v>0.94702508315836598</v>
+      </c>
+      <c r="AP77">
+        <v>18.612661914385601</v>
+      </c>
+      <c r="AQ77">
+        <v>18.612661914385601</v>
+      </c>
+      <c r="AR77">
+        <v>0.94702508315836598</v>
+      </c>
+      <c r="AS77">
+        <v>394.26644516420419</v>
+      </c>
+      <c r="AT77">
+        <v>-0.1221518040832998</v>
+      </c>
+      <c r="AU77">
+        <v>0.2</v>
+      </c>
+      <c r="AV77" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR77">
+        <v>18.612661914385601</v>
+      </c>
+      <c r="BS77">
+        <v>0.94702508315836598</v>
+      </c>
+      <c r="BT77">
+        <v>18.612661914385601</v>
+      </c>
+      <c r="BU77">
+        <v>18.612661914385601</v>
+      </c>
+      <c r="BV77">
+        <v>0.94702508315836598</v>
+      </c>
+      <c r="BW77">
+        <v>394.26644516420419</v>
+      </c>
+      <c r="BX77">
+        <v>-0.1221518040832998</v>
+      </c>
+    </row>
+    <row r="78" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>254</v>
+      </c>
+      <c r="B78" t="s">
+        <v>255</v>
+      </c>
+      <c r="C78">
+        <v>6</v>
+      </c>
+      <c r="D78" t="s">
+        <v>97</v>
+      </c>
+      <c r="E78" t="s">
+        <v>79</v>
+      </c>
+      <c r="F78">
+        <v>16590</v>
+      </c>
+      <c r="G78">
+        <v>4.5</v>
+      </c>
+      <c r="H78" t="s">
+        <v>199</v>
+      </c>
+      <c r="I78" t="s">
+        <v>81</v>
+      </c>
+      <c r="J78">
+        <v>5</v>
+      </c>
+      <c r="K78">
+        <v>5</v>
+      </c>
+      <c r="L78" t="s">
+        <v>82</v>
+      </c>
+      <c r="M78" t="b">
+        <v>1</v>
+      </c>
+      <c r="N78" t="b">
+        <v>0</v>
+      </c>
+      <c r="O78" t="b">
+        <v>0</v>
+      </c>
+      <c r="P78" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>243</v>
+      </c>
+      <c r="R78">
+        <v>1</v>
+      </c>
+      <c r="S78" t="s">
+        <v>85</v>
+      </c>
+      <c r="T78" t="s">
+        <v>86</v>
+      </c>
+      <c r="U78" t="s">
+        <v>87</v>
+      </c>
+      <c r="V78">
+        <v>5</v>
+      </c>
+      <c r="W78" t="s">
+        <v>201</v>
+      </c>
+      <c r="X78" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z78">
+        <v>4000</v>
+      </c>
+      <c r="AA78">
+        <v>4000</v>
+      </c>
+      <c r="AC78">
+        <v>256</v>
+      </c>
+      <c r="AD78" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE78">
+        <v>0.15</v>
+      </c>
+      <c r="AF78" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG78">
+        <v>80</v>
+      </c>
+      <c r="AH78">
+        <v>50</v>
+      </c>
+      <c r="AI78">
+        <v>30</v>
+      </c>
+      <c r="AJ78">
+        <v>4.7547869048884202E-2</v>
+      </c>
+      <c r="AK78">
+        <v>18.49291590390904</v>
+      </c>
+      <c r="AL78">
+        <v>0.94455458100378642</v>
+      </c>
+      <c r="AM78">
+        <v>-0.22972247103040749</v>
+      </c>
+      <c r="AN78">
+        <v>25.542025950437331</v>
+      </c>
+      <c r="AO78">
+        <v>0.92730289160598356</v>
+      </c>
+      <c r="AP78">
+        <v>25.542025950437331</v>
+      </c>
+      <c r="AQ78">
+        <v>25.542025950437331</v>
+      </c>
+      <c r="AR78">
+        <v>0.92730289160598356</v>
+      </c>
+      <c r="AS78">
+        <v>438.67513980547648</v>
+      </c>
+      <c r="AT78">
+        <v>-0.2485467773809473</v>
+      </c>
+      <c r="AU78">
+        <v>0.2</v>
+      </c>
+      <c r="AV78" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR78">
+        <v>25.542025950437331</v>
+      </c>
+      <c r="BS78">
+        <v>0.92730289160598356</v>
+      </c>
+      <c r="BT78">
+        <v>25.542025950437331</v>
+      </c>
+      <c r="BU78">
+        <v>25.542025950437331</v>
+      </c>
+      <c r="BV78">
+        <v>0.92730289160598356</v>
+      </c>
+      <c r="BW78">
+        <v>438.67513980547648</v>
+      </c>
+      <c r="BX78">
+        <v>-0.2485467773809473</v>
+      </c>
+    </row>
+    <row r="79" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>256</v>
+      </c>
+      <c r="B79" t="s">
+        <v>257</v>
+      </c>
+      <c r="C79">
+        <v>7</v>
+      </c>
+      <c r="D79" t="s">
+        <v>97</v>
+      </c>
+      <c r="E79" t="s">
+        <v>79</v>
+      </c>
+      <c r="F79">
+        <v>16590</v>
+      </c>
+      <c r="G79">
+        <v>4.5</v>
+      </c>
+      <c r="H79" t="s">
+        <v>199</v>
+      </c>
+      <c r="I79" t="s">
+        <v>81</v>
+      </c>
+      <c r="J79">
+        <v>5</v>
+      </c>
+      <c r="K79">
+        <v>5</v>
+      </c>
+      <c r="L79" t="s">
+        <v>82</v>
+      </c>
+      <c r="M79" t="b">
+        <v>1</v>
+      </c>
+      <c r="N79" t="b">
+        <v>0</v>
+      </c>
+      <c r="O79" t="b">
+        <v>0</v>
+      </c>
+      <c r="P79" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>243</v>
+      </c>
+      <c r="R79">
+        <v>1</v>
+      </c>
+      <c r="S79" t="s">
+        <v>85</v>
+      </c>
+      <c r="T79" t="s">
+        <v>86</v>
+      </c>
+      <c r="U79" t="s">
+        <v>87</v>
+      </c>
+      <c r="V79">
+        <v>5</v>
+      </c>
+      <c r="W79" t="s">
+        <v>201</v>
+      </c>
+      <c r="X79" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z79">
+        <v>4000</v>
+      </c>
+      <c r="AA79">
+        <v>4000</v>
+      </c>
+      <c r="AC79">
+        <v>256</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE79">
+        <v>0.15</v>
+      </c>
+      <c r="AF79" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG79">
+        <v>80</v>
+      </c>
+      <c r="AH79">
+        <v>50</v>
+      </c>
+      <c r="AI79">
+        <v>30</v>
+      </c>
+      <c r="AJ79">
+        <v>4.2665844382620999E-2</v>
+      </c>
+      <c r="AK79">
+        <v>14.275541520505699</v>
+      </c>
+      <c r="AL79">
+        <v>0.95719910342343717</v>
+      </c>
+      <c r="AM79">
+        <v>-0.86998739325692354</v>
+      </c>
+      <c r="AN79">
+        <v>18.850041147916372</v>
+      </c>
+      <c r="AO79">
+        <v>0.9463494600146124</v>
+      </c>
+      <c r="AP79">
+        <v>18.850041147916372</v>
+      </c>
+      <c r="AQ79">
+        <v>18.850041147916372</v>
+      </c>
+      <c r="AR79">
+        <v>0.9463494600146124</v>
+      </c>
+      <c r="AS79">
+        <v>643.83061484306597</v>
+      </c>
+      <c r="AT79">
+        <v>-0.83245542407066808</v>
+      </c>
+      <c r="AU79">
+        <v>0.2</v>
+      </c>
+      <c r="AV79" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR79">
+        <v>18.850041147916372</v>
+      </c>
+      <c r="BS79">
+        <v>0.9463494600146124</v>
+      </c>
+      <c r="BT79">
+        <v>18.850041147916372</v>
+      </c>
+      <c r="BU79">
+        <v>18.850041147916372</v>
+      </c>
+      <c r="BV79">
+        <v>0.9463494600146124</v>
+      </c>
+      <c r="BW79">
+        <v>643.83061484306597</v>
+      </c>
+      <c r="BX79">
+        <v>-0.83245542407066808</v>
+      </c>
+    </row>
+    <row r="80" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>258</v>
+      </c>
+      <c r="B80" t="s">
+        <v>259</v>
+      </c>
+      <c r="C80">
+        <v>8</v>
+      </c>
+      <c r="D80" t="s">
+        <v>97</v>
+      </c>
+      <c r="E80" t="s">
+        <v>79</v>
+      </c>
+      <c r="F80">
+        <v>16590</v>
+      </c>
+      <c r="G80">
+        <v>4.5</v>
+      </c>
+      <c r="H80" t="s">
+        <v>199</v>
+      </c>
+      <c r="I80" t="s">
+        <v>81</v>
+      </c>
+      <c r="J80">
+        <v>5</v>
+      </c>
+      <c r="K80">
+        <v>5</v>
+      </c>
+      <c r="L80" t="s">
+        <v>82</v>
+      </c>
+      <c r="M80" t="b">
+        <v>1</v>
+      </c>
+      <c r="N80" t="b">
+        <v>0</v>
+      </c>
+      <c r="O80" t="b">
+        <v>0</v>
+      </c>
+      <c r="P80" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>243</v>
+      </c>
+      <c r="R80">
+        <v>1</v>
+      </c>
+      <c r="S80" t="s">
+        <v>85</v>
+      </c>
+      <c r="T80" t="s">
+        <v>86</v>
+      </c>
+      <c r="U80" t="s">
+        <v>87</v>
+      </c>
+      <c r="V80">
+        <v>5</v>
+      </c>
+      <c r="W80" t="s">
+        <v>201</v>
+      </c>
+      <c r="X80" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z80">
+        <v>4000</v>
+      </c>
+      <c r="AA80">
+        <v>4000</v>
+      </c>
+      <c r="AC80">
+        <v>256</v>
+      </c>
+      <c r="AD80" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE80">
+        <v>0.15</v>
+      </c>
+      <c r="AF80" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG80">
+        <v>80</v>
+      </c>
+      <c r="AH80">
+        <v>50</v>
+      </c>
+      <c r="AI80">
+        <v>30</v>
+      </c>
+      <c r="AJ80">
+        <v>5.0567721633465401E-2</v>
+      </c>
+      <c r="AK80">
+        <v>17.592795485020378</v>
+      </c>
+      <c r="AL80">
+        <v>0.94725332002534757</v>
+      </c>
+      <c r="AM80">
+        <v>-0.54362116488562262</v>
+      </c>
+      <c r="AN80">
+        <v>20.482780348111639</v>
+      </c>
+      <c r="AO80">
+        <v>0.94170239643218245</v>
+      </c>
+      <c r="AP80">
+        <v>20.482780348111639</v>
+      </c>
+      <c r="AQ80">
+        <v>20.482780348111639</v>
+      </c>
+      <c r="AR80">
+        <v>0.94170239643218245</v>
+      </c>
+      <c r="AS80">
+        <v>524.0942034894714</v>
+      </c>
+      <c r="AT80">
+        <v>-0.49166449026716608</v>
+      </c>
+      <c r="AU80">
+        <v>0.2</v>
+      </c>
+      <c r="AV80" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR80">
+        <v>20.482780348111639</v>
+      </c>
+      <c r="BS80">
+        <v>0.94170239643218245</v>
+      </c>
+      <c r="BT80">
+        <v>20.482780348111639</v>
+      </c>
+      <c r="BU80">
+        <v>20.482780348111639</v>
+      </c>
+      <c r="BV80">
+        <v>0.94170239643218245</v>
+      </c>
+      <c r="BW80">
+        <v>524.0942034894714</v>
+      </c>
+      <c r="BX80">
+        <v>-0.49166449026716608</v>
+      </c>
+    </row>
+    <row r="81" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>260</v>
+      </c>
+      <c r="B81" t="s">
+        <v>261</v>
+      </c>
+      <c r="C81">
+        <v>9</v>
+      </c>
+      <c r="D81" t="s">
+        <v>78</v>
+      </c>
+      <c r="E81" t="s">
+        <v>79</v>
+      </c>
+      <c r="F81">
+        <v>16590</v>
+      </c>
+      <c r="G81">
+        <v>4.5</v>
+      </c>
+      <c r="H81" t="s">
+        <v>199</v>
+      </c>
+      <c r="I81" t="s">
+        <v>81</v>
+      </c>
+      <c r="J81">
+        <v>5</v>
+      </c>
+      <c r="K81">
+        <v>5</v>
+      </c>
+      <c r="L81" t="s">
+        <v>82</v>
+      </c>
+      <c r="M81" t="b">
+        <v>1</v>
+      </c>
+      <c r="N81" t="b">
+        <v>0</v>
+      </c>
+      <c r="O81" t="b">
+        <v>0</v>
+      </c>
+      <c r="P81" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>243</v>
+      </c>
+      <c r="R81">
+        <v>1</v>
+      </c>
+      <c r="S81" t="s">
+        <v>85</v>
+      </c>
+      <c r="T81" t="s">
+        <v>86</v>
+      </c>
+      <c r="U81" t="s">
+        <v>87</v>
+      </c>
+      <c r="V81">
+        <v>5</v>
+      </c>
+      <c r="W81" t="s">
+        <v>201</v>
+      </c>
+      <c r="X81" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z81">
+        <v>4000</v>
+      </c>
+      <c r="AA81">
+        <v>4000</v>
+      </c>
+      <c r="AC81">
+        <v>256</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE81">
+        <v>0.15</v>
+      </c>
+      <c r="AF81" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG81">
+        <v>80</v>
+      </c>
+      <c r="AH81">
+        <v>50</v>
+      </c>
+      <c r="AI81">
+        <v>30</v>
+      </c>
+      <c r="AJ81">
+        <v>5.5327297988010601E-2</v>
+      </c>
+      <c r="AK81">
+        <v>22.630352938106601</v>
+      </c>
+      <c r="AL81">
+        <v>0.93214972656527983</v>
+      </c>
+      <c r="AM81">
+        <v>-0.70482432609290857</v>
+      </c>
+      <c r="AN81">
+        <v>24.027946791284968</v>
+      </c>
+      <c r="AO81">
+        <v>0.93161222779425623</v>
+      </c>
+      <c r="AP81">
+        <v>24.027946791284968</v>
+      </c>
+      <c r="AQ81">
+        <v>24.027946791284968</v>
+      </c>
+      <c r="AR81">
+        <v>0.93161222779425623</v>
+      </c>
+      <c r="AS81">
+        <v>566.71954488558868</v>
+      </c>
+      <c r="AT81">
+        <v>-0.61298372586023953</v>
+      </c>
+      <c r="AU81">
+        <v>0.2</v>
+      </c>
+      <c r="AV81" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR81">
+        <v>24.027946791284968</v>
+      </c>
+      <c r="BS81">
+        <v>0.93161222779425623</v>
+      </c>
+      <c r="BT81">
+        <v>24.027946791284968</v>
+      </c>
+      <c r="BU81">
+        <v>24.027946791284968</v>
+      </c>
+      <c r="BV81">
+        <v>0.93161222779425623</v>
+      </c>
+      <c r="BW81">
+        <v>566.71954488558868</v>
+      </c>
+      <c r="BX81">
+        <v>-0.61298372586023953</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -13943,16 +21597,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE4BF2F-2951-40B4-8DBE-D07ED8E874D4}">
-  <dimension ref="A3:D9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="3">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>192</v>
       </c>
@@ -13965,8 +21636,17 @@
       <c r="D3" t="s">
         <v>194</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H3" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>111</v>
       </c>
@@ -13979,8 +21659,17 @@
       <c r="D4" s="4">
         <v>10</v>
       </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.97600020254956232</v>
+      </c>
+      <c r="H4" s="4">
+        <v>-3.5092325791814316</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>133</v>
       </c>
@@ -13993,8 +21682,17 @@
       <c r="D5" s="4">
         <v>10</v>
       </c>
+      <c r="F5" s="3">
+        <v>3</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.95830888223024946</v>
+      </c>
+      <c r="H5" s="4">
+        <v>-0.43012243694181035</v>
+      </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>153</v>
       </c>
@@ -14007,8 +21705,17 @@
       <c r="D6" s="4">
         <v>10</v>
       </c>
+      <c r="F6" s="3">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.94329048918159564</v>
+      </c>
+      <c r="H6" s="4">
+        <v>-0.71503681859817225</v>
+      </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>173</v>
       </c>
@@ -14021,8 +21728,17 @@
       <c r="D7" s="4">
         <v>10</v>
       </c>
+      <c r="F7" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0.95919985798713581</v>
+      </c>
+      <c r="H7" s="4">
+        <v>-1.5514639449071381</v>
+      </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>80</v>
       </c>
@@ -14036,18 +21752,32 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.97600020254956232</v>
+      </c>
+      <c r="C9" s="4">
+        <v>-3.5092325791814316</v>
+      </c>
+      <c r="D9" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B9" s="4">
-        <v>0.78093667652373033</v>
-      </c>
-      <c r="C9" s="4">
-        <v>-2.0124861560577343</v>
-      </c>
-      <c r="D9" s="4">
-        <v>50</v>
+      <c r="B10" s="4">
+        <v>0.81344726419470226</v>
+      </c>
+      <c r="C10" s="4">
+        <v>-2.2619438932450175</v>
+      </c>
+      <c r="D10" s="4">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
